--- a/research/traditional_assets/database/data/argentina/argentina_steel.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_steel.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2455761971459171</v>
+        <v>0.2447459304559064</v>
       </c>
       <c r="C2">
-        <v>4184.625033208518</v>
+        <v>4160.000479733977</v>
       </c>
       <c r="D2">
-        <v>4129.425033208518</v>
+        <v>4146.658479733977</v>
       </c>
       <c r="E2">
-        <v>-264.3</v>
+        <v>-222.442</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>41.858</v>
       </c>
       <c r="G2">
         <v>55.2</v>
@@ -1445,28 +1445,28 @@
         <v>197.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.1054574</v>
       </c>
       <c r="N2">
-        <v>197.6</v>
+        <v>195.4945426</v>
       </c>
       <c r="O2">
-        <v>69.16</v>
+        <v>68.42308990999999</v>
       </c>
       <c r="P2">
-        <v>128.44</v>
+        <v>127.07145269</v>
       </c>
       <c r="Q2">
-        <v>199.14</v>
+        <v>197.77145269</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2455761971459171</v>
+        <v>0.2468878590463701</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161359</v>
+        <v>0.9880194934141713</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>93.85134080604053</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2447459304559064</v>
+        <v>0.2439156637658957</v>
       </c>
       <c r="C3">
-        <v>4160.000479733977</v>
+        <v>4135.520370735274</v>
       </c>
       <c r="D3">
-        <v>4146.658479733977</v>
+        <v>4164.036370735274</v>
       </c>
       <c r="E3">
-        <v>-222.442</v>
+        <v>-180.584</v>
       </c>
       <c r="F3">
-        <v>41.858</v>
+        <v>83.71600000000001</v>
       </c>
       <c r="G3">
         <v>55.2</v>
@@ -1527,28 +1527,28 @@
         <v>197.6</v>
       </c>
       <c r="M3">
-        <v>2.1054574</v>
+        <v>4.2109148</v>
       </c>
       <c r="N3">
-        <v>195.4945426</v>
+        <v>193.3890852</v>
       </c>
       <c r="O3">
-        <v>68.42308990999999</v>
+        <v>67.68617981999999</v>
       </c>
       <c r="P3">
-        <v>127.07145269</v>
+        <v>125.70290538</v>
       </c>
       <c r="Q3">
-        <v>197.77145269</v>
+        <v>196.40290538</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2468878590463701</v>
+        <v>0.2482262895570365</v>
       </c>
       <c r="T3">
-        <v>0.9880194934141713</v>
+        <v>0.9945957006570643</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>93.85134080604053</v>
+        <v>46.92567040302026</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2439156637658957</v>
+        <v>0.243085397075885</v>
       </c>
       <c r="C4">
-        <v>4135.520370735274</v>
+        <v>4111.186529876587</v>
       </c>
       <c r="D4">
-        <v>4164.036370735274</v>
+        <v>4181.560529876587</v>
       </c>
       <c r="E4">
-        <v>-180.584</v>
+        <v>-138.726</v>
       </c>
       <c r="F4">
-        <v>83.71600000000001</v>
+        <v>125.574</v>
       </c>
       <c r="G4">
         <v>55.2</v>
@@ -1609,28 +1609,28 @@
         <v>197.6</v>
       </c>
       <c r="M4">
-        <v>4.2109148</v>
+        <v>6.3163722</v>
       </c>
       <c r="N4">
-        <v>193.3890852</v>
+        <v>191.2836278</v>
       </c>
       <c r="O4">
-        <v>67.68617981999999</v>
+        <v>66.94926973</v>
       </c>
       <c r="P4">
-        <v>125.70290538</v>
+        <v>124.33435807</v>
       </c>
       <c r="Q4">
-        <v>196.40290538</v>
+        <v>195.03435807</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2482262895570365</v>
+        <v>0.2495923165730773</v>
       </c>
       <c r="T4">
-        <v>0.9945957006570643</v>
+        <v>1.001307499801873</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>46.92567040302026</v>
+        <v>31.28378026868018</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.243085397075885</v>
+        <v>0.2422551303858743</v>
       </c>
       <c r="C5">
-        <v>4111.186529876587</v>
+        <v>4087.000811651061</v>
       </c>
       <c r="D5">
-        <v>4181.560529876587</v>
+        <v>4199.232811651061</v>
       </c>
       <c r="E5">
-        <v>-138.726</v>
+        <v>-96.86799999999999</v>
       </c>
       <c r="F5">
-        <v>125.574</v>
+        <v>167.432</v>
       </c>
       <c r="G5">
         <v>55.2</v>
@@ -1691,28 +1691,28 @@
         <v>197.6</v>
       </c>
       <c r="M5">
-        <v>6.3163722</v>
+        <v>8.421829600000001</v>
       </c>
       <c r="N5">
-        <v>191.2836278</v>
+        <v>189.1781704</v>
       </c>
       <c r="O5">
-        <v>66.94926973</v>
+        <v>66.21235964</v>
       </c>
       <c r="P5">
-        <v>124.33435807</v>
+        <v>122.96581076</v>
       </c>
       <c r="Q5">
-        <v>195.03435807</v>
+        <v>193.66581076</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2495923165730773</v>
+        <v>0.2509868024852857</v>
       </c>
       <c r="T5">
-        <v>1.001307499801873</v>
+        <v>1.008159128095531</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>31.28378026868018</v>
+        <v>23.46283520151013</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2422551303858743</v>
+        <v>0.2414248636958635</v>
       </c>
       <c r="C6">
-        <v>4087.000811651061</v>
+        <v>4062.965102035039</v>
       </c>
       <c r="D6">
-        <v>4199.232811651061</v>
+        <v>4217.055102035039</v>
       </c>
       <c r="E6">
-        <v>-96.86799999999999</v>
+        <v>-55.00999999999999</v>
       </c>
       <c r="F6">
-        <v>167.432</v>
+        <v>209.29</v>
       </c>
       <c r="G6">
         <v>55.2</v>
@@ -1773,28 +1773,28 @@
         <v>197.6</v>
       </c>
       <c r="M6">
-        <v>8.421829600000001</v>
+        <v>10.527287</v>
       </c>
       <c r="N6">
-        <v>189.1781704</v>
+        <v>187.072713</v>
       </c>
       <c r="O6">
-        <v>66.21235964</v>
+        <v>65.47544954999999</v>
       </c>
       <c r="P6">
-        <v>122.96581076</v>
+        <v>121.59726345</v>
       </c>
       <c r="Q6">
-        <v>193.66581076</v>
+        <v>192.29726345</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2509868024852857</v>
+        <v>0.2524106459956458</v>
       </c>
       <c r="T6">
-        <v>1.008159128095531</v>
+        <v>1.015155001195372</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.46283520151013</v>
+        <v>18.7702681612081</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2414248636958635</v>
+        <v>0.2405945970058529</v>
       </c>
       <c r="C7">
-        <v>4062.965102035039</v>
+        <v>4039.081319159008</v>
       </c>
       <c r="D7">
-        <v>4217.055102035039</v>
+        <v>4235.029319159008</v>
       </c>
       <c r="E7">
-        <v>-55.00999999999999</v>
+        <v>-13.15199999999999</v>
       </c>
       <c r="F7">
-        <v>209.29</v>
+        <v>251.148</v>
       </c>
       <c r="G7">
         <v>55.2</v>
@@ -1855,28 +1855,28 @@
         <v>197.6</v>
       </c>
       <c r="M7">
-        <v>10.527287</v>
+        <v>12.6327444</v>
       </c>
       <c r="N7">
-        <v>187.072713</v>
+        <v>184.9672556</v>
       </c>
       <c r="O7">
-        <v>65.47544954999999</v>
+        <v>64.73853946</v>
       </c>
       <c r="P7">
-        <v>121.59726345</v>
+        <v>120.22871614</v>
       </c>
       <c r="Q7">
-        <v>192.29726345</v>
+        <v>190.92871614</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2524106459956458</v>
+        <v>0.2538647840487797</v>
       </c>
       <c r="T7">
-        <v>1.015155001195372</v>
+        <v>1.02229972265904</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.7702681612081</v>
+        <v>15.64189013434009</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2405945970058529</v>
+        <v>0.2397643303158421</v>
       </c>
       <c r="C8">
-        <v>4039.081319159008</v>
+        <v>4015.35141399578</v>
       </c>
       <c r="D8">
-        <v>4235.029319159008</v>
+        <v>4253.15741399578</v>
       </c>
       <c r="E8">
-        <v>-13.15200000000002</v>
+        <v>28.70599999999996</v>
       </c>
       <c r="F8">
-        <v>251.148</v>
+        <v>293.006</v>
       </c>
       <c r="G8">
         <v>55.2</v>
@@ -1937,28 +1937,28 @@
         <v>197.6</v>
       </c>
       <c r="M8">
-        <v>12.6327444</v>
+        <v>14.7382018</v>
       </c>
       <c r="N8">
-        <v>184.9672556</v>
+        <v>182.8617982</v>
       </c>
       <c r="O8">
-        <v>64.73853946</v>
+        <v>64.00162937</v>
       </c>
       <c r="P8">
-        <v>120.22871614</v>
+        <v>118.86016883</v>
       </c>
       <c r="Q8">
-        <v>190.92871614</v>
+        <v>189.56016883</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2538647840487797</v>
+        <v>0.2553501938880023</v>
       </c>
       <c r="T8">
-        <v>1.02229972265904</v>
+        <v>1.029598094046656</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.64189013434009</v>
+        <v>13.40733440086294</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2397643303158421</v>
+        <v>0.2390120636258314</v>
       </c>
       <c r="C9">
-        <v>4015.351413995781</v>
+        <v>3990.052983775632</v>
       </c>
       <c r="D9">
-        <v>4253.157413995781</v>
+        <v>4269.716983775632</v>
       </c>
       <c r="E9">
-        <v>28.70600000000002</v>
+        <v>70.56400000000002</v>
       </c>
       <c r="F9">
-        <v>293.006</v>
+        <v>334.864</v>
       </c>
       <c r="G9">
         <v>55.2</v>
@@ -2019,45 +2019,45 @@
         <v>197.6</v>
       </c>
       <c r="M9">
-        <v>14.7382018</v>
+        <v>17.3459552</v>
       </c>
       <c r="N9">
-        <v>182.8617982</v>
+        <v>180.2540448</v>
       </c>
       <c r="O9">
-        <v>64.00162936999999</v>
+        <v>63.08891568</v>
       </c>
       <c r="P9">
-        <v>118.86016883</v>
+        <v>117.16512912</v>
       </c>
       <c r="Q9">
-        <v>189.56016883</v>
+        <v>187.86512912</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2553501938880023</v>
+        <v>0.2568678952454689</v>
       </c>
       <c r="T9">
-        <v>1.029598094046656</v>
+        <v>1.037055125681831</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.35</v>
       </c>
       <c r="W9">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.40733440086293</v>
+        <v>11.39170473586834</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2390120636258314</v>
+        <v>0.2381915469358207</v>
       </c>
       <c r="C10">
-        <v>3990.052983775632</v>
+        <v>3966.404588628899</v>
       </c>
       <c r="D10">
-        <v>4269.716983775632</v>
+        <v>4287.926588628899</v>
       </c>
       <c r="E10">
-        <v>70.56400000000002</v>
+        <v>112.422</v>
       </c>
       <c r="F10">
-        <v>334.864</v>
+        <v>376.722</v>
       </c>
       <c r="G10">
         <v>55.2</v>
@@ -2101,28 +2101,28 @@
         <v>197.6</v>
       </c>
       <c r="M10">
-        <v>17.3459552</v>
+        <v>19.5141996</v>
       </c>
       <c r="N10">
-        <v>180.2540448</v>
+        <v>178.0858004</v>
       </c>
       <c r="O10">
-        <v>63.08891568</v>
+        <v>62.33003013999999</v>
       </c>
       <c r="P10">
-        <v>117.16512912</v>
+        <v>115.75577026</v>
       </c>
       <c r="Q10">
-        <v>187.86512912</v>
+        <v>186.45577026</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2568678952454689</v>
+        <v>0.2584189526767261</v>
       </c>
       <c r="T10">
-        <v>1.037055125681831</v>
+        <v>1.044676048122173</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.39170473586834</v>
+        <v>10.1259597652163</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2381915469358207</v>
+        <v>0.23748153024581</v>
       </c>
       <c r="C11">
-        <v>3966.404588628899</v>
+        <v>3940.429701830067</v>
       </c>
       <c r="D11">
-        <v>4287.926588628899</v>
+        <v>4303.809701830067</v>
       </c>
       <c r="E11">
-        <v>112.422</v>
+        <v>154.28</v>
       </c>
       <c r="F11">
-        <v>376.722</v>
+        <v>418.58</v>
       </c>
       <c r="G11">
         <v>55.2</v>
@@ -2183,45 +2183,45 @@
         <v>197.6</v>
       </c>
       <c r="M11">
-        <v>19.5141996</v>
+        <v>22.39403</v>
       </c>
       <c r="N11">
-        <v>178.0858004</v>
+        <v>175.20597</v>
       </c>
       <c r="O11">
-        <v>62.33003013999999</v>
+        <v>61.3220895</v>
       </c>
       <c r="P11">
-        <v>115.75577026</v>
+        <v>113.8838805</v>
       </c>
       <c r="Q11">
-        <v>186.45577026</v>
+        <v>184.5838805</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2584189526767261</v>
+        <v>0.2600044780509</v>
       </c>
       <c r="T11">
-        <v>1.044676048122173</v>
+        <v>1.052466324394523</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.35</v>
       </c>
       <c r="W11">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.1259597652163</v>
+        <v>8.823780266437083</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.23748153024581</v>
+        <v>0.2366720635557993</v>
       </c>
       <c r="C12">
-        <v>3940.429701830067</v>
+        <v>3916.823668769994</v>
       </c>
       <c r="D12">
-        <v>4303.809701830067</v>
+        <v>4322.061668769994</v>
       </c>
       <c r="E12">
-        <v>154.28</v>
+        <v>196.138</v>
       </c>
       <c r="F12">
-        <v>418.58</v>
+        <v>460.438</v>
       </c>
       <c r="G12">
         <v>55.2</v>
@@ -2265,28 +2265,28 @@
         <v>197.6</v>
       </c>
       <c r="M12">
-        <v>22.39403</v>
+        <v>24.633433</v>
       </c>
       <c r="N12">
-        <v>175.20597</v>
+        <v>172.966567</v>
       </c>
       <c r="O12">
-        <v>61.32208949999999</v>
+        <v>60.53829844999999</v>
       </c>
       <c r="P12">
-        <v>113.8838805</v>
+        <v>112.42826855</v>
       </c>
       <c r="Q12">
-        <v>184.5838805</v>
+        <v>183.12826855</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2600044780509</v>
+        <v>0.2616256332087633</v>
       </c>
       <c r="T12">
-        <v>1.052466324394523</v>
+        <v>1.060431663055017</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.82378026643708</v>
+        <v>8.02161842403371</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2366720635557993</v>
+        <v>0.2359249968657886</v>
       </c>
       <c r="C13">
-        <v>3916.823668769994</v>
+        <v>3891.948539818715</v>
       </c>
       <c r="D13">
-        <v>4322.061668769994</v>
+        <v>4339.044539818715</v>
       </c>
       <c r="E13">
-        <v>196.138</v>
+        <v>237.996</v>
       </c>
       <c r="F13">
-        <v>460.438</v>
+        <v>502.296</v>
       </c>
       <c r="G13">
         <v>55.2</v>
@@ -2347,45 +2347,45 @@
         <v>197.6</v>
       </c>
       <c r="M13">
-        <v>24.633433</v>
+        <v>27.2746728</v>
       </c>
       <c r="N13">
-        <v>172.966567</v>
+        <v>170.3253272</v>
       </c>
       <c r="O13">
-        <v>60.53829844999999</v>
+        <v>59.61386452</v>
       </c>
       <c r="P13">
-        <v>112.42826855</v>
+        <v>110.71146268</v>
       </c>
       <c r="Q13">
-        <v>183.12826855</v>
+        <v>181.41146268</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2616256332087633</v>
+        <v>0.2632836328020325</v>
       </c>
       <c r="T13">
-        <v>1.060431663055017</v>
+        <v>1.068578032139612</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.35</v>
       </c>
       <c r="W13">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>8.02161842403371</v>
+        <v>7.24481651710227</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2359249968657886</v>
+        <v>0.2351207301757779</v>
       </c>
       <c r="C14">
-        <v>3891.948539818715</v>
+        <v>3868.523539662996</v>
       </c>
       <c r="D14">
-        <v>4339.044539818715</v>
+        <v>4357.477539662996</v>
       </c>
       <c r="E14">
-        <v>237.996</v>
+        <v>279.854</v>
       </c>
       <c r="F14">
-        <v>502.296</v>
+        <v>544.154</v>
       </c>
       <c r="G14">
         <v>55.2</v>
@@ -2429,28 +2429,28 @@
         <v>197.6</v>
       </c>
       <c r="M14">
-        <v>27.2746728</v>
+        <v>29.5475622</v>
       </c>
       <c r="N14">
-        <v>170.3253272</v>
+        <v>168.0524378</v>
       </c>
       <c r="O14">
-        <v>59.61386452</v>
+        <v>58.81835323</v>
       </c>
       <c r="P14">
-        <v>110.71146268</v>
+        <v>109.23408457</v>
       </c>
       <c r="Q14">
-        <v>181.41146268</v>
+        <v>179.93408457</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2632836328020325</v>
+        <v>0.2649797473284803</v>
       </c>
       <c r="T14">
-        <v>1.068578032139612</v>
+        <v>1.076911674076726</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.24481651710227</v>
+        <v>6.687522938863633</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2351207301757779</v>
+        <v>0.2343164634857672</v>
       </c>
       <c r="C15">
-        <v>3868.523539662996</v>
+        <v>3845.255820706991</v>
       </c>
       <c r="D15">
-        <v>4357.477539662996</v>
+        <v>4376.067820706991</v>
       </c>
       <c r="E15">
-        <v>279.854</v>
+        <v>321.712</v>
       </c>
       <c r="F15">
-        <v>544.154</v>
+        <v>586.0120000000001</v>
       </c>
       <c r="G15">
         <v>55.2</v>
@@ -2511,28 +2511,28 @@
         <v>197.6</v>
       </c>
       <c r="M15">
-        <v>29.5475622</v>
+        <v>31.82045160000001</v>
       </c>
       <c r="N15">
-        <v>168.0524378</v>
+        <v>165.7795484</v>
       </c>
       <c r="O15">
-        <v>58.81835323</v>
+        <v>58.02284193999999</v>
       </c>
       <c r="P15">
-        <v>109.23408457</v>
+        <v>107.75670646</v>
       </c>
       <c r="Q15">
-        <v>179.93408457</v>
+        <v>178.45670646</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2649797473284803</v>
+        <v>0.266715306378799</v>
       </c>
       <c r="T15">
-        <v>1.076911674076726</v>
+        <v>1.085439121640285</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.687522938863633</v>
+        <v>6.209842728944801</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2343164634857672</v>
+        <v>0.2336096967957565</v>
       </c>
       <c r="C16">
-        <v>3845.255820706991</v>
+        <v>3819.865867999923</v>
       </c>
       <c r="D16">
-        <v>4376.067820706991</v>
+        <v>4392.535867999923</v>
       </c>
       <c r="E16">
-        <v>321.712</v>
+        <v>363.5700000000001</v>
       </c>
       <c r="F16">
-        <v>586.0120000000001</v>
+        <v>627.8700000000001</v>
       </c>
       <c r="G16">
         <v>55.2</v>
@@ -2593,45 +2593,45 @@
         <v>197.6</v>
       </c>
       <c r="M16">
-        <v>31.82045160000001</v>
+        <v>34.72121100000001</v>
       </c>
       <c r="N16">
-        <v>165.7795484</v>
+        <v>162.878789</v>
       </c>
       <c r="O16">
-        <v>58.02284193999999</v>
+        <v>57.00757614999999</v>
       </c>
       <c r="P16">
-        <v>107.75670646</v>
+        <v>105.87121285</v>
       </c>
       <c r="Q16">
-        <v>178.45670646</v>
+        <v>176.57121285</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.266715306378799</v>
+        <v>0.2684917021126547</v>
       </c>
       <c r="T16">
-        <v>1.085439121640285</v>
+        <v>1.094167215028869</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.35</v>
       </c>
       <c r="W16">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.209842728944801</v>
+        <v>5.691045741463336</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2336096967957565</v>
+        <v>0.2328119301057458</v>
       </c>
       <c r="C17">
-        <v>3819.865867999923</v>
+        <v>3796.745810537524</v>
       </c>
       <c r="D17">
-        <v>4392.535867999923</v>
+        <v>4411.273810537525</v>
       </c>
       <c r="E17">
-        <v>363.57</v>
+        <v>405.4280000000001</v>
       </c>
       <c r="F17">
-        <v>627.87</v>
+        <v>669.7280000000001</v>
       </c>
       <c r="G17">
         <v>55.2</v>
@@ -2675,28 +2675,28 @@
         <v>197.6</v>
       </c>
       <c r="M17">
-        <v>34.721211</v>
+        <v>37.03595840000001</v>
       </c>
       <c r="N17">
-        <v>162.878789</v>
+        <v>160.5640416</v>
       </c>
       <c r="O17">
-        <v>57.00757614999999</v>
+        <v>56.19741455999999</v>
       </c>
       <c r="P17">
-        <v>105.87121285</v>
+        <v>104.36662704</v>
       </c>
       <c r="Q17">
-        <v>176.57121285</v>
+        <v>175.06662704</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2684917021126547</v>
+        <v>0.2703103929830307</v>
       </c>
       <c r="T17">
-        <v>1.094167215028869</v>
+        <v>1.1031031201648</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.691045741463337</v>
+        <v>5.335355382621878</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2328119301057458</v>
+        <v>0.232014163415735</v>
       </c>
       <c r="C18">
-        <v>3796.745810537524</v>
+        <v>3773.786304841134</v>
       </c>
       <c r="D18">
-        <v>4411.273810537525</v>
+        <v>4430.172304841134</v>
       </c>
       <c r="E18">
-        <v>405.4280000000001</v>
+        <v>447.2860000000001</v>
       </c>
       <c r="F18">
-        <v>669.7280000000001</v>
+        <v>711.5860000000001</v>
       </c>
       <c r="G18">
         <v>55.2</v>
@@ -2757,28 +2757,28 @@
         <v>197.6</v>
       </c>
       <c r="M18">
-        <v>37.03595840000001</v>
+        <v>39.35070580000001</v>
       </c>
       <c r="N18">
-        <v>160.5640416</v>
+        <v>158.2492942</v>
       </c>
       <c r="O18">
-        <v>56.19741455999999</v>
+        <v>55.38725296999999</v>
       </c>
       <c r="P18">
-        <v>104.36662704</v>
+        <v>102.86204123</v>
       </c>
       <c r="Q18">
-        <v>175.06662704</v>
+        <v>173.56204123</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2703103929830307</v>
+        <v>0.2721729077298012</v>
       </c>
       <c r="T18">
-        <v>1.1031031201648</v>
+        <v>1.112254348316055</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.335355382621878</v>
+        <v>5.021510948350003</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.232014163415735</v>
+        <v>0.2312163967257243</v>
       </c>
       <c r="C19">
-        <v>3773.786304841134</v>
+        <v>3750.98942326551</v>
       </c>
       <c r="D19">
-        <v>4430.172304841134</v>
+        <v>4449.23342326551</v>
       </c>
       <c r="E19">
-        <v>447.2860000000001</v>
+        <v>489.1440000000001</v>
       </c>
       <c r="F19">
-        <v>711.5860000000001</v>
+        <v>753.4440000000001</v>
       </c>
       <c r="G19">
         <v>55.2</v>
@@ -2839,28 +2839,28 @@
         <v>197.6</v>
       </c>
       <c r="M19">
-        <v>39.35070580000001</v>
+        <v>41.66545320000001</v>
       </c>
       <c r="N19">
-        <v>158.2492942</v>
+        <v>155.9345468</v>
       </c>
       <c r="O19">
-        <v>55.38725296999999</v>
+        <v>54.57709137999999</v>
       </c>
       <c r="P19">
-        <v>102.86204123</v>
+        <v>101.35745542</v>
       </c>
       <c r="Q19">
-        <v>173.56204123</v>
+        <v>172.05745542</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2721729077298012</v>
+        <v>0.2740808496655175</v>
       </c>
       <c r="T19">
-        <v>1.112254348316055</v>
+        <v>1.121628777153926</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.021510948350003</v>
+        <v>4.742538117886114</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2312163967257244</v>
+        <v>0.2307273800357137</v>
       </c>
       <c r="C20">
-        <v>3750.989423265509</v>
+        <v>3720.896849246832</v>
       </c>
       <c r="D20">
-        <v>4449.233423265509</v>
+        <v>4460.998849246832</v>
       </c>
       <c r="E20">
-        <v>489.1439999999999</v>
+        <v>531.002</v>
       </c>
       <c r="F20">
-        <v>753.444</v>
+        <v>795.302</v>
       </c>
       <c r="G20">
         <v>55.2</v>
@@ -2921,45 +2921,45 @@
         <v>197.6</v>
       </c>
       <c r="M20">
-        <v>41.6654532</v>
+        <v>45.96845560000001</v>
       </c>
       <c r="N20">
-        <v>155.9345468</v>
+        <v>151.6315444</v>
       </c>
       <c r="O20">
-        <v>54.57709137999999</v>
+        <v>53.07104054</v>
       </c>
       <c r="P20">
-        <v>101.35745542</v>
+        <v>98.56050386</v>
       </c>
       <c r="Q20">
-        <v>172.05745542</v>
+        <v>169.26050386</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2740808496655175</v>
+        <v>0.2760359012786588</v>
       </c>
       <c r="T20">
-        <v>1.121628777153926</v>
+        <v>1.13123467337051</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.35</v>
       </c>
       <c r="W20">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.742538117886115</v>
+        <v>4.298599929469894</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2307273800357137</v>
+        <v>0.2299458633457029</v>
       </c>
       <c r="C21">
-        <v>3720.896849246832</v>
+        <v>3697.971368237281</v>
       </c>
       <c r="D21">
-        <v>4460.998849246832</v>
+        <v>4479.931368237281</v>
       </c>
       <c r="E21">
-        <v>531.002</v>
+        <v>572.8600000000001</v>
       </c>
       <c r="F21">
-        <v>795.302</v>
+        <v>837.1600000000001</v>
       </c>
       <c r="G21">
         <v>55.2</v>
@@ -3003,28 +3003,28 @@
         <v>197.6</v>
       </c>
       <c r="M21">
-        <v>45.96845560000001</v>
+        <v>48.38784800000001</v>
       </c>
       <c r="N21">
-        <v>151.6315444</v>
+        <v>149.212152</v>
       </c>
       <c r="O21">
-        <v>53.07104054</v>
+        <v>52.2242532</v>
       </c>
       <c r="P21">
-        <v>98.56050386</v>
+        <v>96.98789880000001</v>
       </c>
       <c r="Q21">
-        <v>169.26050386</v>
+        <v>167.6878988</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2760359012786588</v>
+        <v>0.2780398291821287</v>
       </c>
       <c r="T21">
-        <v>1.13123467337051</v>
+        <v>1.141080716992508</v>
       </c>
       <c r="U21">
         <v>0.0578</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.298599929469894</v>
+        <v>4.083669932996401</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2299458633457029</v>
+        <v>0.2296420966556923</v>
       </c>
       <c r="C22">
-        <v>3697.971368237281</v>
+        <v>3663.515665904464</v>
       </c>
       <c r="D22">
-        <v>4479.931368237281</v>
+        <v>4487.333665904464</v>
       </c>
       <c r="E22">
-        <v>572.8600000000001</v>
+        <v>614.7180000000001</v>
       </c>
       <c r="F22">
-        <v>837.1600000000001</v>
+        <v>879.0180000000001</v>
       </c>
       <c r="G22">
         <v>55.2</v>
@@ -3085,45 +3085,45 @@
         <v>197.6</v>
       </c>
       <c r="M22">
-        <v>48.38784800000001</v>
+        <v>53.88380340000001</v>
       </c>
       <c r="N22">
-        <v>149.212152</v>
+        <v>143.7161966</v>
       </c>
       <c r="O22">
-        <v>52.2242532</v>
+        <v>50.30066880999999</v>
       </c>
       <c r="P22">
-        <v>96.98789880000001</v>
+        <v>93.41552779</v>
       </c>
       <c r="Q22">
-        <v>167.6878988</v>
+        <v>164.11552779</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2780398291821287</v>
+        <v>0.2800944894375851</v>
       </c>
       <c r="T22">
-        <v>1.141080716992508</v>
+        <v>1.151176027541646</v>
       </c>
       <c r="U22">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.083669932996401</v>
+        <v>3.66715019229693</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2296420966556923</v>
+        <v>0.2288833299656815</v>
       </c>
       <c r="C23">
-        <v>3663.515665904464</v>
+        <v>3640.254876875504</v>
       </c>
       <c r="D23">
-        <v>4487.333665904464</v>
+        <v>4505.930876875505</v>
       </c>
       <c r="E23">
-        <v>614.7180000000001</v>
+        <v>656.576</v>
       </c>
       <c r="F23">
-        <v>879.018</v>
+        <v>920.8760000000001</v>
       </c>
       <c r="G23">
         <v>55.2</v>
@@ -3167,28 +3167,28 @@
         <v>197.6</v>
       </c>
       <c r="M23">
-        <v>53.88380340000001</v>
+        <v>56.44969880000001</v>
       </c>
       <c r="N23">
-        <v>143.7161966</v>
+        <v>141.1503012</v>
       </c>
       <c r="O23">
-        <v>50.30066880999999</v>
+        <v>49.40260542</v>
       </c>
       <c r="P23">
-        <v>93.41552779</v>
+        <v>91.74769578</v>
       </c>
       <c r="Q23">
-        <v>164.11552779</v>
+        <v>162.44769578</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2800944894375851</v>
+        <v>0.2822018332893352</v>
       </c>
       <c r="T23">
-        <v>1.151176027541646</v>
+        <v>1.161530192207427</v>
       </c>
       <c r="U23">
         <v>0.0613</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.66715019229693</v>
+        <v>3.500461547192524</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2288833299656815</v>
+        <v>0.2285431632756708</v>
       </c>
       <c r="C24">
-        <v>3640.254876875504</v>
+        <v>3606.784427820386</v>
       </c>
       <c r="D24">
-        <v>4505.930876875505</v>
+        <v>4514.318427820386</v>
       </c>
       <c r="E24">
-        <v>656.576</v>
+        <v>698.434</v>
       </c>
       <c r="F24">
-        <v>920.8760000000001</v>
+        <v>962.734</v>
       </c>
       <c r="G24">
         <v>55.2</v>
@@ -3249,45 +3249,45 @@
         <v>197.6</v>
       </c>
       <c r="M24">
-        <v>56.44969880000001</v>
+        <v>61.71124940000001</v>
       </c>
       <c r="N24">
-        <v>141.1503012</v>
+        <v>135.8887506</v>
       </c>
       <c r="O24">
-        <v>49.40260542</v>
+        <v>47.56106270999999</v>
       </c>
       <c r="P24">
-        <v>91.74769578</v>
+        <v>88.32768788999999</v>
       </c>
       <c r="Q24">
-        <v>162.44769578</v>
+        <v>159.02768789</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2822018332893352</v>
+        <v>0.284363913345027</v>
       </c>
       <c r="T24">
-        <v>1.161530192207427</v>
+        <v>1.172153296215178</v>
       </c>
       <c r="U24">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.500461547192524</v>
+        <v>3.20200938923139</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2285431632756708</v>
+        <v>0.2278025965856601</v>
       </c>
       <c r="C25">
-        <v>3606.784427820386</v>
+        <v>3583.295142984139</v>
       </c>
       <c r="D25">
-        <v>4514.318427820386</v>
+        <v>4532.687142984139</v>
       </c>
       <c r="E25">
-        <v>698.434</v>
+        <v>740.2920000000001</v>
       </c>
       <c r="F25">
-        <v>962.734</v>
+        <v>1004.592</v>
       </c>
       <c r="G25">
         <v>55.2</v>
@@ -3331,28 +3331,28 @@
         <v>197.6</v>
       </c>
       <c r="M25">
-        <v>61.71124940000001</v>
+        <v>64.39434720000001</v>
       </c>
       <c r="N25">
-        <v>135.8887506</v>
+        <v>133.2056528</v>
       </c>
       <c r="O25">
-        <v>47.56106270999999</v>
+        <v>46.62197848</v>
       </c>
       <c r="P25">
-        <v>88.32768788999999</v>
+        <v>86.58367432</v>
       </c>
       <c r="Q25">
-        <v>159.02768789</v>
+        <v>157.28367432</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.284363913345027</v>
+        <v>0.2865828902442896</v>
       </c>
       <c r="T25">
-        <v>1.172153296215178</v>
+        <v>1.183055955591553</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.20200938923139</v>
+        <v>3.068592331346748</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2278025965856601</v>
+        <v>0.2283295298956494</v>
       </c>
       <c r="C26">
-        <v>3583.295142984139</v>
+        <v>3528.352006344802</v>
       </c>
       <c r="D26">
-        <v>4532.687142984139</v>
+        <v>4519.602006344802</v>
       </c>
       <c r="E26">
-        <v>740.2919999999999</v>
+        <v>782.1500000000001</v>
       </c>
       <c r="F26">
-        <v>1004.592</v>
+        <v>1046.45</v>
       </c>
       <c r="G26">
         <v>55.2</v>
@@ -3413,45 +3413,45 @@
         <v>197.6</v>
       </c>
       <c r="M26">
-        <v>64.3943472</v>
+        <v>75.239755</v>
       </c>
       <c r="N26">
-        <v>133.2056528</v>
+        <v>122.360245</v>
       </c>
       <c r="O26">
-        <v>46.62197848</v>
+        <v>42.82608575</v>
       </c>
       <c r="P26">
-        <v>86.58367432</v>
+        <v>79.53415924999999</v>
       </c>
       <c r="Q26">
-        <v>157.28367432</v>
+        <v>150.23415925</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2865828902442896</v>
+        <v>0.2888610398608659</v>
       </c>
       <c r="T26">
-        <v>1.183055955591553</v>
+        <v>1.194249352551299</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.35</v>
       </c>
       <c r="W26">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.068592331346749</v>
+        <v>2.626271178049423</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2283295298956494</v>
+        <v>0.2276396632056386</v>
       </c>
       <c r="C27">
-        <v>3528.352006344802</v>
+        <v>3503.640556340097</v>
       </c>
       <c r="D27">
-        <v>4519.602006344802</v>
+        <v>4536.748556340097</v>
       </c>
       <c r="E27">
-        <v>782.1500000000001</v>
+        <v>824.008</v>
       </c>
       <c r="F27">
-        <v>1046.45</v>
+        <v>1088.308</v>
       </c>
       <c r="G27">
         <v>55.2</v>
@@ -3495,28 +3495,28 @@
         <v>197.6</v>
       </c>
       <c r="M27">
-        <v>75.239755</v>
+        <v>78.24934520000001</v>
       </c>
       <c r="N27">
-        <v>122.360245</v>
+        <v>119.3506548</v>
       </c>
       <c r="O27">
-        <v>42.82608575</v>
+        <v>41.77272917999999</v>
       </c>
       <c r="P27">
-        <v>79.53415924999999</v>
+        <v>77.57792562</v>
       </c>
       <c r="Q27">
-        <v>150.23415925</v>
+        <v>148.27792562</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2888610398608659</v>
+        <v>0.2912007610887009</v>
       </c>
       <c r="T27">
-        <v>1.194249352551299</v>
+        <v>1.205745273753199</v>
       </c>
       <c r="U27">
         <v>0.07190000000000001</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.626271178049423</v>
+        <v>2.525260748124445</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2276396632056386</v>
+        <v>0.227634246515628</v>
       </c>
       <c r="C28">
-        <v>3503.640556340097</v>
+        <v>3461.917702282387</v>
       </c>
       <c r="D28">
-        <v>4536.748556340097</v>
+        <v>4536.883702282387</v>
       </c>
       <c r="E28">
-        <v>824.008</v>
+        <v>865.8660000000002</v>
       </c>
       <c r="F28">
-        <v>1088.308</v>
+        <v>1130.166</v>
       </c>
       <c r="G28">
         <v>55.2</v>
@@ -3577,45 +3577,45 @@
         <v>197.6</v>
       </c>
       <c r="M28">
-        <v>78.24934520000001</v>
+        <v>85.66658280000001</v>
       </c>
       <c r="N28">
-        <v>119.3506548</v>
+        <v>111.9334172</v>
       </c>
       <c r="O28">
-        <v>41.77272917999999</v>
+        <v>39.17669601999999</v>
       </c>
       <c r="P28">
-        <v>77.57792562</v>
+        <v>72.75672118</v>
       </c>
       <c r="Q28">
-        <v>148.27792562</v>
+        <v>143.45672118</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2912007610887009</v>
+        <v>0.2936045842679835</v>
       </c>
       <c r="T28">
-        <v>1.205745273753199</v>
+        <v>1.217556151700358</v>
       </c>
       <c r="U28">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.525260748124445</v>
+        <v>2.306617044143378</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.227634246515628</v>
+        <v>0.2269697298256172</v>
       </c>
       <c r="C29">
-        <v>3461.917702282387</v>
+        <v>3436.7006441423</v>
       </c>
       <c r="D29">
-        <v>4536.883702282387</v>
+        <v>4553.524644142301</v>
       </c>
       <c r="E29">
-        <v>865.8660000000002</v>
+        <v>907.7240000000002</v>
       </c>
       <c r="F29">
-        <v>1130.166</v>
+        <v>1172.024</v>
       </c>
       <c r="G29">
         <v>55.2</v>
@@ -3659,28 +3659,28 @@
         <v>197.6</v>
       </c>
       <c r="M29">
-        <v>85.66658280000001</v>
+        <v>88.83941920000002</v>
       </c>
       <c r="N29">
-        <v>111.9334172</v>
+        <v>108.7605808</v>
       </c>
       <c r="O29">
-        <v>39.17669601999999</v>
+        <v>38.06620327999999</v>
       </c>
       <c r="P29">
-        <v>72.75672118</v>
+        <v>70.69437751999999</v>
       </c>
       <c r="Q29">
-        <v>143.45672118</v>
+        <v>141.39437752</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2936045842679835</v>
+        <v>0.2960751803133573</v>
       </c>
       <c r="T29">
-        <v>1.217556151700358</v>
+        <v>1.229695109590492</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.306617044143378</v>
+        <v>2.2242378639954</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2269697298256172</v>
+        <v>0.2263052131356066</v>
       </c>
       <c r="C30">
-        <v>3436.7006441423</v>
+        <v>3411.606110813671</v>
       </c>
       <c r="D30">
-        <v>4553.524644142301</v>
+        <v>4570.288110813672</v>
       </c>
       <c r="E30">
-        <v>907.7240000000002</v>
+        <v>949.5820000000003</v>
       </c>
       <c r="F30">
-        <v>1172.024</v>
+        <v>1213.882</v>
       </c>
       <c r="G30">
         <v>55.2</v>
@@ -3741,28 +3741,28 @@
         <v>197.6</v>
       </c>
       <c r="M30">
-        <v>88.83941920000002</v>
+        <v>92.01225560000003</v>
       </c>
       <c r="N30">
-        <v>108.7605808</v>
+        <v>105.5877444</v>
       </c>
       <c r="O30">
-        <v>38.06620327999999</v>
+        <v>36.95571053999998</v>
       </c>
       <c r="P30">
-        <v>70.69437751999999</v>
+        <v>68.63203385999998</v>
       </c>
       <c r="Q30">
-        <v>141.39437752</v>
+        <v>139.33203386</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2960751803133573</v>
+        <v>0.2986153706135304</v>
       </c>
       <c r="T30">
-        <v>1.229695109590492</v>
+        <v>1.242176009956406</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.2242378639954</v>
+        <v>2.147540006616248</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2263052131356066</v>
+        <v>0.2256406964455958</v>
       </c>
       <c r="C31">
-        <v>3411.606110813671</v>
+        <v>3386.635460494906</v>
       </c>
       <c r="D31">
-        <v>4570.288110813672</v>
+        <v>4587.175460494906</v>
       </c>
       <c r="E31">
-        <v>949.5820000000001</v>
+        <v>991.4400000000001</v>
       </c>
       <c r="F31">
-        <v>1213.882</v>
+        <v>1255.74</v>
       </c>
       <c r="G31">
         <v>55.2</v>
@@ -3823,28 +3823,28 @@
         <v>197.6</v>
       </c>
       <c r="M31">
-        <v>92.01225560000002</v>
+        <v>95.18509200000001</v>
       </c>
       <c r="N31">
-        <v>105.5877444</v>
+        <v>102.414908</v>
       </c>
       <c r="O31">
-        <v>36.95571053999999</v>
+        <v>35.84521779999999</v>
       </c>
       <c r="P31">
-        <v>68.63203385999998</v>
+        <v>66.5696902</v>
       </c>
       <c r="Q31">
-        <v>139.33203386</v>
+        <v>137.2696902</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2986153706135304</v>
+        <v>0.3012281377794226</v>
       </c>
       <c r="T31">
-        <v>1.242176009956406</v>
+        <v>1.255013507475631</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.147540006616249</v>
+        <v>2.07595533972904</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2256406964455958</v>
+        <v>0.2249761797555851</v>
       </c>
       <c r="C32">
-        <v>3386.635460494906</v>
+        <v>3361.790071533183</v>
       </c>
       <c r="D32">
-        <v>4587.175460494906</v>
+        <v>4604.188071533184</v>
       </c>
       <c r="E32">
-        <v>991.4400000000001</v>
+        <v>1033.298</v>
       </c>
       <c r="F32">
-        <v>1255.74</v>
+        <v>1297.598</v>
       </c>
       <c r="G32">
         <v>55.2</v>
@@ -3905,28 +3905,28 @@
         <v>197.6</v>
       </c>
       <c r="M32">
-        <v>95.18509200000001</v>
+        <v>98.35792840000001</v>
       </c>
       <c r="N32">
-        <v>102.414908</v>
+        <v>99.24207159999999</v>
       </c>
       <c r="O32">
-        <v>35.84521779999999</v>
+        <v>34.73472506</v>
       </c>
       <c r="P32">
-        <v>66.5696902</v>
+        <v>64.50734653999999</v>
       </c>
       <c r="Q32">
-        <v>137.2696902</v>
+        <v>135.20734654</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.3012281377794226</v>
+        <v>0.303916637326935</v>
       </c>
       <c r="T32">
-        <v>1.255013507475631</v>
+        <v>1.268223106372225</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.07595533972904</v>
+        <v>2.008989038447459</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2249761797555851</v>
+        <v>0.2272652630655744</v>
       </c>
       <c r="C33">
-        <v>3361.790071533183</v>
+        <v>3261.852801194872</v>
       </c>
       <c r="D33">
-        <v>4604.188071533184</v>
+        <v>4546.108801194872</v>
       </c>
       <c r="E33">
-        <v>1033.298</v>
+        <v>1075.156</v>
       </c>
       <c r="F33">
-        <v>1297.598</v>
+        <v>1339.456</v>
       </c>
       <c r="G33">
         <v>55.2</v>
@@ -3987,45 +3987,45 @@
         <v>197.6</v>
       </c>
       <c r="M33">
-        <v>98.35792840000001</v>
+        <v>120.55104</v>
       </c>
       <c r="N33">
-        <v>99.24207159999999</v>
+        <v>77.04895999999999</v>
       </c>
       <c r="O33">
-        <v>34.73472506</v>
+        <v>26.967136</v>
       </c>
       <c r="P33">
-        <v>64.50734653999999</v>
+        <v>50.081824</v>
       </c>
       <c r="Q33">
-        <v>135.20734654</v>
+        <v>120.781824</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.303916637326935</v>
+        <v>0.3066842103905506</v>
       </c>
       <c r="T33">
-        <v>1.268223106372225</v>
+        <v>1.281821222883424</v>
       </c>
       <c r="U33">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V33">
         <v>0.35</v>
       </c>
       <c r="W33">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.008989038447459</v>
+        <v>1.639139736994388</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2272652630655744</v>
+        <v>0.2266930463755636</v>
       </c>
       <c r="C34">
-        <v>3261.852801194872</v>
+        <v>3234.375449775733</v>
       </c>
       <c r="D34">
-        <v>4546.108801194872</v>
+        <v>4560.489449775733</v>
       </c>
       <c r="E34">
-        <v>1075.156</v>
+        <v>1117.014</v>
       </c>
       <c r="F34">
-        <v>1339.456</v>
+        <v>1381.314</v>
       </c>
       <c r="G34">
         <v>55.2</v>
@@ -4069,28 +4069,28 @@
         <v>197.6</v>
       </c>
       <c r="M34">
-        <v>120.55104</v>
+        <v>124.31826</v>
       </c>
       <c r="N34">
-        <v>77.04895999999999</v>
+        <v>73.28173999999999</v>
       </c>
       <c r="O34">
-        <v>26.967136</v>
+        <v>25.64860899999999</v>
       </c>
       <c r="P34">
-        <v>50.081824</v>
+        <v>47.63313099999999</v>
       </c>
       <c r="Q34">
-        <v>120.781824</v>
+        <v>118.333131</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.3066842103905506</v>
+        <v>0.3095343975754682</v>
       </c>
       <c r="T34">
-        <v>1.281821222883424</v>
+        <v>1.295825253320332</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.639139736994388</v>
+        <v>1.589468835873346</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2266930463755636</v>
+        <v>0.226120829685553</v>
       </c>
       <c r="C35">
-        <v>3234.375449775733</v>
+        <v>3206.989367314765</v>
       </c>
       <c r="D35">
-        <v>4560.489449775733</v>
+        <v>4574.961367314766</v>
       </c>
       <c r="E35">
-        <v>1117.014</v>
+        <v>1158.872</v>
       </c>
       <c r="F35">
-        <v>1381.314</v>
+        <v>1423.172</v>
       </c>
       <c r="G35">
         <v>55.2</v>
@@ -4151,28 +4151,28 @@
         <v>197.6</v>
       </c>
       <c r="M35">
-        <v>124.31826</v>
+        <v>128.08548</v>
       </c>
       <c r="N35">
-        <v>73.28173999999999</v>
+        <v>69.51451999999998</v>
       </c>
       <c r="O35">
-        <v>25.64860899999999</v>
+        <v>24.33008199999999</v>
       </c>
       <c r="P35">
-        <v>47.63313099999999</v>
+        <v>45.18443799999999</v>
       </c>
       <c r="Q35">
-        <v>118.333131</v>
+        <v>115.884438</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3095343975754682</v>
+        <v>0.3124709540690197</v>
       </c>
       <c r="T35">
-        <v>1.295825253320332</v>
+        <v>1.310253648315933</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.589468835873346</v>
+        <v>1.542719752465306</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.226120829685553</v>
+        <v>0.2419186010170765</v>
       </c>
       <c r="C36">
-        <v>3206.989367314765</v>
+        <v>2796.608477815365</v>
       </c>
       <c r="D36">
-        <v>4574.961367314766</v>
+        <v>4206.438477815365</v>
       </c>
       <c r="E36">
-        <v>1158.872</v>
+        <v>1200.73</v>
       </c>
       <c r="F36">
-        <v>1423.172</v>
+        <v>1465.03</v>
       </c>
       <c r="G36">
         <v>55.2</v>
@@ -4233,45 +4233,45 @@
         <v>197.6</v>
       </c>
       <c r="M36">
-        <v>128.08548</v>
+        <v>215.0664040000001</v>
       </c>
       <c r="N36">
-        <v>69.51451999999998</v>
+        <v>-17.46640400000007</v>
       </c>
       <c r="O36">
-        <v>24.33008199999999</v>
+        <v>-6.113241400000024</v>
       </c>
       <c r="P36">
-        <v>45.18443799999999</v>
+        <v>-11.35316260000004</v>
       </c>
       <c r="Q36">
-        <v>115.884438</v>
+        <v>59.34683739999997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3124709540690197</v>
+        <v>0.3185555839476615</v>
       </c>
       <c r="T36">
-        <v>1.310253648315933</v>
+        <v>1.340149699518717</v>
       </c>
       <c r="U36">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.35</v>
+        <v>0.3215750982659289</v>
       </c>
       <c r="W36">
-        <v>0.0585</v>
+        <v>0.09959277557456164</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.542719752465306</v>
+        <v>0.9187859950455113</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2419186010170765</v>
+        <v>0.2429286010170765</v>
       </c>
       <c r="C37">
-        <v>2796.608477815365</v>
+        <v>2733.198542476335</v>
       </c>
       <c r="D37">
-        <v>4206.438477815365</v>
+        <v>4184.886542476335</v>
       </c>
       <c r="E37">
-        <v>1200.73</v>
+        <v>1242.588</v>
       </c>
       <c r="F37">
-        <v>1465.03</v>
+        <v>1506.888</v>
       </c>
       <c r="G37">
         <v>55.2</v>
@@ -4315,37 +4315,37 @@
         <v>197.6</v>
       </c>
       <c r="M37">
-        <v>215.0664040000001</v>
+        <v>221.2111584</v>
       </c>
       <c r="N37">
-        <v>-17.46640400000007</v>
+        <v>-23.61115840000005</v>
       </c>
       <c r="O37">
-        <v>-6.113241400000024</v>
+        <v>-8.263905440000018</v>
       </c>
       <c r="P37">
-        <v>-11.35316260000004</v>
+        <v>-15.34725296000003</v>
       </c>
       <c r="Q37">
-        <v>59.34683739999997</v>
+        <v>55.35274703999998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3185555839476615</v>
+        <v>0.3228173899468437</v>
       </c>
       <c r="T37">
-        <v>1.340149699518717</v>
+        <v>1.361089538573697</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.3215750982659289</v>
+        <v>0.312642456647431</v>
       </c>
       <c r="W37">
-        <v>0.09959277557456164</v>
+        <v>0.1009040873641571</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9187859950455113</v>
+        <v>0.8932641618498027</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2429286010170766</v>
+        <v>0.2439386010170765</v>
       </c>
       <c r="C38">
-        <v>2733.198542476334</v>
+        <v>2670.008326612265</v>
       </c>
       <c r="D38">
-        <v>4184.886542476334</v>
+        <v>4163.554326612265</v>
       </c>
       <c r="E38">
-        <v>1242.588</v>
+        <v>1284.446</v>
       </c>
       <c r="F38">
-        <v>1506.888</v>
+        <v>1548.746</v>
       </c>
       <c r="G38">
         <v>55.2</v>
@@ -4397,37 +4397,37 @@
         <v>197.6</v>
       </c>
       <c r="M38">
-        <v>221.2111584</v>
+        <v>227.3559128</v>
       </c>
       <c r="N38">
-        <v>-23.61115840000002</v>
+        <v>-29.75591280000003</v>
       </c>
       <c r="O38">
-        <v>-8.263905440000007</v>
+        <v>-10.41456948000001</v>
       </c>
       <c r="P38">
-        <v>-15.34725296000001</v>
+        <v>-19.34134332000002</v>
       </c>
       <c r="Q38">
-        <v>55.35274704</v>
+        <v>51.35865668</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3228173899468437</v>
+        <v>0.3272144913745714</v>
       </c>
       <c r="T38">
-        <v>1.361089538573697</v>
+        <v>1.382694134424073</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.312642456647431</v>
+        <v>0.3041926605218247</v>
       </c>
       <c r="W38">
-        <v>0.1009040873641571</v>
+        <v>0.1021445174353961</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8932641618498028</v>
+        <v>0.8691218872052136</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2439386010170765</v>
+        <v>0.2449486010170766</v>
       </c>
       <c r="C39">
-        <v>2670.008326612265</v>
+        <v>2607.034487242056</v>
       </c>
       <c r="D39">
-        <v>4163.554326612265</v>
+        <v>4142.438487242056</v>
       </c>
       <c r="E39">
-        <v>1284.446</v>
+        <v>1326.304</v>
       </c>
       <c r="F39">
-        <v>1548.746</v>
+        <v>1590.604</v>
       </c>
       <c r="G39">
         <v>55.2</v>
@@ -4479,37 +4479,37 @@
         <v>197.6</v>
       </c>
       <c r="M39">
-        <v>227.3559128</v>
+        <v>233.5006672</v>
       </c>
       <c r="N39">
-        <v>-29.75591280000003</v>
+        <v>-35.90066720000004</v>
       </c>
       <c r="O39">
-        <v>-10.41456948000001</v>
+        <v>-12.56523352000001</v>
       </c>
       <c r="P39">
-        <v>-19.34134332000002</v>
+        <v>-23.33543368000003</v>
       </c>
       <c r="Q39">
-        <v>51.35865668</v>
+        <v>47.36456631999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3272144913745714</v>
+        <v>0.3317534347838387</v>
       </c>
       <c r="T39">
-        <v>1.382694134424073</v>
+        <v>1.404995652721235</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.3041926605218247</v>
+        <v>0.2961875905080925</v>
       </c>
       <c r="W39">
-        <v>0.1021445174353961</v>
+        <v>0.103319661713412</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8691218872052136</v>
+        <v>0.8462502585945501</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2449486010170766</v>
+        <v>0.2459586010170766</v>
       </c>
       <c r="C40">
-        <v>2607.034487242056</v>
+        <v>2544.273748859319</v>
       </c>
       <c r="D40">
-        <v>4142.438487242056</v>
+        <v>4121.53574885932</v>
       </c>
       <c r="E40">
-        <v>1326.304</v>
+        <v>1368.162</v>
       </c>
       <c r="F40">
-        <v>1590.604</v>
+        <v>1632.462</v>
       </c>
       <c r="G40">
         <v>55.2</v>
@@ -4561,37 +4561,37 @@
         <v>197.6</v>
       </c>
       <c r="M40">
-        <v>233.5006672</v>
+        <v>239.6454216</v>
       </c>
       <c r="N40">
-        <v>-35.90066720000004</v>
+        <v>-42.04542160000005</v>
       </c>
       <c r="O40">
-        <v>-12.56523352000001</v>
+        <v>-14.71589756000002</v>
       </c>
       <c r="P40">
-        <v>-23.33543368000003</v>
+        <v>-27.32952404000004</v>
       </c>
       <c r="Q40">
-        <v>47.36456631999999</v>
+        <v>43.37047595999998</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3317534347838387</v>
+        <v>0.3364411960098033</v>
       </c>
       <c r="T40">
-        <v>1.404995652721235</v>
+        <v>1.428028368339616</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.2961875905080925</v>
+        <v>0.2885930369053208</v>
       </c>
       <c r="W40">
-        <v>0.103319661713412</v>
+        <v>0.1044345421822989</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8462502585945501</v>
+        <v>0.8245515340152025</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2459586010170766</v>
+        <v>0.2469686010170765</v>
       </c>
       <c r="C41">
-        <v>2544.273748859319</v>
+        <v>2481.722901738538</v>
       </c>
       <c r="D41">
-        <v>4121.53574885932</v>
+        <v>4100.842901738538</v>
       </c>
       <c r="E41">
-        <v>1368.162</v>
+        <v>1410.02</v>
       </c>
       <c r="F41">
-        <v>1632.462</v>
+        <v>1674.32</v>
       </c>
       <c r="G41">
         <v>55.2</v>
@@ -4643,37 +4643,37 @@
         <v>197.6</v>
       </c>
       <c r="M41">
-        <v>239.6454216</v>
+        <v>245.7901760000001</v>
       </c>
       <c r="N41">
-        <v>-42.04542160000005</v>
+        <v>-48.19017600000006</v>
       </c>
       <c r="O41">
-        <v>-14.71589756000002</v>
+        <v>-16.86656160000002</v>
       </c>
       <c r="P41">
-        <v>-27.32952404000004</v>
+        <v>-31.32361440000004</v>
       </c>
       <c r="Q41">
-        <v>43.37047595999998</v>
+        <v>39.37638559999998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3364411960098033</v>
+        <v>0.3412852159433</v>
       </c>
       <c r="T41">
-        <v>1.428028368339616</v>
+        <v>1.451828841145276</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.2885930369053208</v>
+        <v>0.2813782109826878</v>
       </c>
       <c r="W41">
-        <v>0.1044345421822989</v>
+        <v>0.1054936786277414</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8245515340152025</v>
+        <v>0.8039377456648225</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2469686010170765</v>
+        <v>0.2761653821391712</v>
       </c>
       <c r="C42">
-        <v>2481.722901738538</v>
+        <v>1920.119219872927</v>
       </c>
       <c r="D42">
-        <v>4100.842901738538</v>
+        <v>3581.097219872927</v>
       </c>
       <c r="E42">
-        <v>1410.02</v>
+        <v>1451.878</v>
       </c>
       <c r="F42">
-        <v>1674.32</v>
+        <v>1716.178</v>
       </c>
       <c r="G42">
         <v>55.2</v>
@@ -4725,45 +4725,45 @@
         <v>197.6</v>
       </c>
       <c r="M42">
-        <v>245.7901760000001</v>
+        <v>344.6085424</v>
       </c>
       <c r="N42">
-        <v>-48.19017600000006</v>
+        <v>-147.0085424</v>
       </c>
       <c r="O42">
-        <v>-16.86656160000002</v>
+        <v>-51.45298984000001</v>
       </c>
       <c r="P42">
-        <v>-31.32361440000004</v>
+        <v>-95.55555256000002</v>
       </c>
       <c r="Q42">
-        <v>39.37638559999998</v>
+        <v>-24.85555256000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3412852159433</v>
+        <v>0.3565422215052112</v>
       </c>
       <c r="T42">
-        <v>1.451828841145276</v>
+        <v>1.526792187902182</v>
       </c>
       <c r="U42">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.2813782109826878</v>
+        <v>0.2006914846577523</v>
       </c>
       <c r="W42">
-        <v>0.1054936786277414</v>
+        <v>0.1605011498807233</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.8039377456648225</v>
+        <v>0.5734042418792924</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2761653821391712</v>
+        <v>0.2777153821391712</v>
       </c>
       <c r="C43">
-        <v>1920.119219872927</v>
+        <v>1854.327056301698</v>
       </c>
       <c r="D43">
-        <v>3581.097219872927</v>
+        <v>3557.163056301698</v>
       </c>
       <c r="E43">
-        <v>1451.878</v>
+        <v>1493.736</v>
       </c>
       <c r="F43">
-        <v>1716.178</v>
+        <v>1758.036</v>
       </c>
       <c r="G43">
         <v>55.2</v>
@@ -4807,37 +4807,37 @@
         <v>197.6</v>
       </c>
       <c r="M43">
-        <v>344.6085424</v>
+        <v>353.0136288</v>
       </c>
       <c r="N43">
-        <v>-147.0085424</v>
+        <v>-155.4136288000001</v>
       </c>
       <c r="O43">
-        <v>-51.45298984000001</v>
+        <v>-54.39477008000001</v>
       </c>
       <c r="P43">
-        <v>-95.55555256000002</v>
+        <v>-101.01885872</v>
       </c>
       <c r="Q43">
-        <v>-24.85555256000001</v>
+        <v>-30.31885872000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3565422215052112</v>
+        <v>0.3618998460139218</v>
       </c>
       <c r="T43">
-        <v>1.526792187902182</v>
+        <v>1.553116191141874</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.2006914846577523</v>
+        <v>0.1959131159754249</v>
       </c>
       <c r="W43">
-        <v>0.1605011498807233</v>
+        <v>0.1614606463121347</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5734042418792924</v>
+        <v>0.5597517599297854</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2777153821391712</v>
+        <v>0.2792653821391712</v>
       </c>
       <c r="C44">
-        <v>1854.327056301698</v>
+        <v>1788.852695337395</v>
       </c>
       <c r="D44">
-        <v>3557.163056301698</v>
+        <v>3533.546695337395</v>
       </c>
       <c r="E44">
-        <v>1493.736</v>
+        <v>1535.594</v>
       </c>
       <c r="F44">
-        <v>1758.036</v>
+        <v>1799.894</v>
       </c>
       <c r="G44">
         <v>55.2</v>
@@ -4889,37 +4889,37 @@
         <v>197.6</v>
       </c>
       <c r="M44">
-        <v>353.0136288</v>
+        <v>361.4187152</v>
       </c>
       <c r="N44">
-        <v>-155.4136288000001</v>
+        <v>-163.8187152</v>
       </c>
       <c r="O44">
-        <v>-54.39477008000001</v>
+        <v>-57.33655032</v>
       </c>
       <c r="P44">
-        <v>-101.01885872</v>
+        <v>-106.48216488</v>
       </c>
       <c r="Q44">
-        <v>-30.31885872000002</v>
+        <v>-35.78216488</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3618998460139217</v>
+        <v>0.3674454573474993</v>
       </c>
       <c r="T44">
-        <v>1.553116191141874</v>
+        <v>1.580363843618047</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1959131159754249</v>
+        <v>0.1913569969992522</v>
       </c>
       <c r="W44">
-        <v>0.1614606463121347</v>
+        <v>0.1623755150025502</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5597517599297854</v>
+        <v>0.5467342771407206</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2792653821391712</v>
+        <v>0.2808153821391712</v>
       </c>
       <c r="C45">
-        <v>1788.852695337395</v>
+        <v>1723.689848957042</v>
       </c>
       <c r="D45">
-        <v>3533.546695337395</v>
+        <v>3510.241848957043</v>
       </c>
       <c r="E45">
-        <v>1535.594</v>
+        <v>1577.452</v>
       </c>
       <c r="F45">
-        <v>1799.894</v>
+        <v>1841.752</v>
       </c>
       <c r="G45">
         <v>55.2</v>
@@ -4971,37 +4971,37 @@
         <v>197.6</v>
       </c>
       <c r="M45">
-        <v>361.4187152</v>
+        <v>369.8238016</v>
       </c>
       <c r="N45">
-        <v>-163.8187152</v>
+        <v>-172.2238016</v>
       </c>
       <c r="O45">
-        <v>-57.33655032</v>
+        <v>-60.27833056000001</v>
       </c>
       <c r="P45">
-        <v>-106.48216488</v>
+        <v>-111.94547104</v>
       </c>
       <c r="Q45">
-        <v>-35.78216488</v>
+        <v>-41.24547104000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3674454573474993</v>
+        <v>0.3731891262287047</v>
       </c>
       <c r="T45">
-        <v>1.580363843618047</v>
+        <v>1.608584626539799</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1913569969992522</v>
+        <v>0.1870079743401783</v>
       </c>
       <c r="W45">
-        <v>0.1623755150025502</v>
+        <v>0.1632487987524922</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5467342771407206</v>
+        <v>0.5343084981147952</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2808153821391712</v>
+        <v>0.2823653821391712</v>
       </c>
       <c r="C46">
-        <v>1723.689848957042</v>
+        <v>1658.832393936686</v>
       </c>
       <c r="D46">
-        <v>3510.241848957043</v>
+        <v>3487.242393936687</v>
       </c>
       <c r="E46">
-        <v>1577.452</v>
+        <v>1619.31</v>
       </c>
       <c r="F46">
-        <v>1841.752</v>
+        <v>1883.61</v>
       </c>
       <c r="G46">
         <v>55.2</v>
@@ -5053,37 +5053,37 @@
         <v>197.6</v>
       </c>
       <c r="M46">
-        <v>369.8238016</v>
+        <v>378.228888</v>
       </c>
       <c r="N46">
-        <v>-172.2238016</v>
+        <v>-180.628888</v>
       </c>
       <c r="O46">
-        <v>-60.27833056000001</v>
+        <v>-63.22011080000001</v>
       </c>
       <c r="P46">
-        <v>-111.94547104</v>
+        <v>-117.4087772</v>
       </c>
       <c r="Q46">
-        <v>-41.24547104000001</v>
+        <v>-46.70877720000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3731891262287047</v>
+        <v>0.3791416557964993</v>
       </c>
       <c r="T46">
-        <v>1.608584626539799</v>
+        <v>1.637831619749613</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1870079743401783</v>
+        <v>0.1828522415770632</v>
       </c>
       <c r="W46">
-        <v>0.1632487987524922</v>
+        <v>0.1640832698913257</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5343084981147952</v>
+        <v>0.5224349759344664</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2823653821391712</v>
+        <v>0.2839153821391712</v>
       </c>
       <c r="C47">
-        <v>1658.832393936686</v>
+        <v>1594.274366487629</v>
       </c>
       <c r="D47">
-        <v>3487.242393936687</v>
+        <v>3464.542366487629</v>
       </c>
       <c r="E47">
-        <v>1619.31</v>
+        <v>1661.168</v>
       </c>
       <c r="F47">
-        <v>1883.61</v>
+        <v>1925.468</v>
       </c>
       <c r="G47">
         <v>55.2</v>
@@ -5135,37 +5135,37 @@
         <v>197.6</v>
       </c>
       <c r="M47">
-        <v>378.228888</v>
+        <v>386.6339744</v>
       </c>
       <c r="N47">
-        <v>-180.628888</v>
+        <v>-189.0339744</v>
       </c>
       <c r="O47">
-        <v>-63.22011080000001</v>
+        <v>-66.16189104</v>
       </c>
       <c r="P47">
-        <v>-117.4087772</v>
+        <v>-122.87208336</v>
       </c>
       <c r="Q47">
-        <v>-46.70877720000001</v>
+        <v>-52.17208335999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3791416557964993</v>
+        <v>0.3853146494223604</v>
       </c>
       <c r="T47">
-        <v>1.637831619749613</v>
+        <v>1.668161834930161</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1828522415770632</v>
+        <v>0.1788771928471271</v>
       </c>
       <c r="W47">
-        <v>0.1640832698913257</v>
+        <v>0.1648814596762969</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5224349759344664</v>
+        <v>0.5110776938489345</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2839153821391712</v>
+        <v>0.2854653821391712</v>
       </c>
       <c r="C48">
-        <v>1594.274366487629</v>
+        <v>1530.009957100822</v>
       </c>
       <c r="D48">
-        <v>3464.542366487629</v>
+        <v>3442.135957100822</v>
       </c>
       <c r="E48">
-        <v>1661.168</v>
+        <v>1703.026</v>
       </c>
       <c r="F48">
-        <v>1925.468</v>
+        <v>1967.326</v>
       </c>
       <c r="G48">
         <v>55.2</v>
@@ -5217,37 +5217,37 @@
         <v>197.6</v>
       </c>
       <c r="M48">
-        <v>386.6339744</v>
+        <v>395.0390608000001</v>
       </c>
       <c r="N48">
-        <v>-189.0339744</v>
+        <v>-197.4390608000001</v>
       </c>
       <c r="O48">
-        <v>-66.16189104</v>
+        <v>-69.10367128000003</v>
       </c>
       <c r="P48">
-        <v>-122.87208336</v>
+        <v>-128.33538952</v>
       </c>
       <c r="Q48">
-        <v>-52.17208335999999</v>
+        <v>-57.63538952000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3853146494223604</v>
+        <v>0.3917205862039144</v>
       </c>
       <c r="T48">
-        <v>1.668161834930161</v>
+        <v>1.699636586532617</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1788771928471271</v>
+        <v>0.1750712951269754</v>
       </c>
       <c r="W48">
-        <v>0.1648814596762969</v>
+        <v>0.1656456839385033</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5110776938489345</v>
+        <v>0.5002037003627868</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2854653821391712</v>
+        <v>0.3062553313589528</v>
       </c>
       <c r="C49">
-        <v>1530.009957100822</v>
+        <v>1213.395316941724</v>
       </c>
       <c r="D49">
-        <v>3442.135957100822</v>
+        <v>3167.379316941724</v>
       </c>
       <c r="E49">
-        <v>1703.026</v>
+        <v>1744.884</v>
       </c>
       <c r="F49">
-        <v>1967.326</v>
+        <v>2009.184</v>
       </c>
       <c r="G49">
         <v>55.2</v>
@@ -5299,45 +5299,45 @@
         <v>197.6</v>
       </c>
       <c r="M49">
-        <v>395.0390608000001</v>
+        <v>473.7655872000001</v>
       </c>
       <c r="N49">
-        <v>-197.4390608000001</v>
+        <v>-276.1655872000001</v>
       </c>
       <c r="O49">
-        <v>-69.10367128000003</v>
+        <v>-96.65795552000003</v>
       </c>
       <c r="P49">
-        <v>-128.33538952</v>
+        <v>-179.5076316800001</v>
       </c>
       <c r="Q49">
-        <v>-57.63538952000002</v>
+        <v>-108.8076316800001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3917205862039144</v>
+        <v>0.4030651152074157</v>
       </c>
       <c r="T49">
-        <v>1.699636586532617</v>
+        <v>1.755376479792295</v>
       </c>
       <c r="U49">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1750712951269754</v>
+        <v>0.1459793658900854</v>
       </c>
       <c r="W49">
-        <v>0.1656456839385033</v>
+        <v>0.2013780655231179</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.5002037003627868</v>
+        <v>0.4170839025431012</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.3062553313589528</v>
+        <v>0.3081553313589527</v>
       </c>
       <c r="C50">
-        <v>1213.395316941724</v>
+        <v>1148.598881991626</v>
       </c>
       <c r="D50">
-        <v>3167.379316941724</v>
+        <v>3144.440881991626</v>
       </c>
       <c r="E50">
-        <v>1744.884</v>
+        <v>1786.742</v>
       </c>
       <c r="F50">
-        <v>2009.184</v>
+        <v>2051.042</v>
       </c>
       <c r="G50">
         <v>55.2</v>
@@ -5381,37 +5381,37 @@
         <v>197.6</v>
       </c>
       <c r="M50">
-        <v>473.7655872</v>
+        <v>483.6357036</v>
       </c>
       <c r="N50">
-        <v>-276.1655872</v>
+        <v>-286.0357036</v>
       </c>
       <c r="O50">
-        <v>-96.65795552</v>
+        <v>-100.11249626</v>
       </c>
       <c r="P50">
-        <v>-179.50763168</v>
+        <v>-185.92320734</v>
       </c>
       <c r="Q50">
-        <v>-108.80763168</v>
+        <v>-115.22320734</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.4030651152074157</v>
+        <v>0.410070313544816</v>
       </c>
       <c r="T50">
-        <v>1.755376479792295</v>
+        <v>1.789795626454889</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1459793658900854</v>
+        <v>0.1430001951576347</v>
       </c>
       <c r="W50">
-        <v>0.2013780655231179</v>
+        <v>0.2020805539818297</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4170839025431015</v>
+        <v>0.4085719861646707</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.3081553313589527</v>
+        <v>0.3100553313589527</v>
       </c>
       <c r="C51">
-        <v>1148.598881991626</v>
+        <v>1084.132302459624</v>
       </c>
       <c r="D51">
-        <v>3144.440881991626</v>
+        <v>3121.832302459625</v>
       </c>
       <c r="E51">
-        <v>1786.742</v>
+        <v>1828.6</v>
       </c>
       <c r="F51">
-        <v>2051.042</v>
+        <v>2092.9</v>
       </c>
       <c r="G51">
         <v>55.2</v>
@@ -5463,37 +5463,37 @@
         <v>197.6</v>
       </c>
       <c r="M51">
-        <v>483.6357036</v>
+        <v>493.50582</v>
       </c>
       <c r="N51">
-        <v>-286.0357036</v>
+        <v>-295.9058200000001</v>
       </c>
       <c r="O51">
-        <v>-100.11249626</v>
+        <v>-103.567037</v>
       </c>
       <c r="P51">
-        <v>-185.92320734</v>
+        <v>-192.338783</v>
       </c>
       <c r="Q51">
-        <v>-115.22320734</v>
+        <v>-121.638783</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.410070313544816</v>
+        <v>0.4173557198157123</v>
       </c>
       <c r="T51">
-        <v>1.789795626454889</v>
+        <v>1.825591538983987</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1430001951576347</v>
+        <v>0.140140191254482</v>
       </c>
       <c r="W51">
-        <v>0.2020805539818297</v>
+        <v>0.2027549429021931</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4085719861646707</v>
+        <v>0.4004005464413772</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.3100553313589527</v>
+        <v>0.3119553313589527</v>
       </c>
       <c r="C52">
-        <v>1084.132302459624</v>
+        <v>1019.988514140495</v>
       </c>
       <c r="D52">
-        <v>3121.832302459625</v>
+        <v>3099.546514140496</v>
       </c>
       <c r="E52">
-        <v>1828.6</v>
+        <v>1870.458</v>
       </c>
       <c r="F52">
-        <v>2092.9</v>
+        <v>2134.758</v>
       </c>
       <c r="G52">
         <v>55.2</v>
@@ -5545,37 +5545,37 @@
         <v>197.6</v>
       </c>
       <c r="M52">
-        <v>493.50582</v>
+        <v>503.3759364000001</v>
       </c>
       <c r="N52">
-        <v>-295.9058200000001</v>
+        <v>-305.7759364000001</v>
       </c>
       <c r="O52">
-        <v>-103.567037</v>
+        <v>-107.02157774</v>
       </c>
       <c r="P52">
-        <v>-192.338783</v>
+        <v>-198.7543586600001</v>
       </c>
       <c r="Q52">
-        <v>-121.638783</v>
+        <v>-128.05435866</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.4173557198157123</v>
+        <v>0.4249384896078697</v>
       </c>
       <c r="T52">
-        <v>1.825591538983987</v>
+        <v>1.862848509167333</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.140140191254482</v>
+        <v>0.1373923443671393</v>
       </c>
       <c r="W52">
-        <v>0.2027549429021931</v>
+        <v>0.2034028851982286</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4004005464413772</v>
+        <v>0.3925495553346835</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.3119553313589527</v>
+        <v>0.3138553313589527</v>
       </c>
       <c r="C53">
-        <v>1019.988514140495</v>
+        <v>956.1606531158668</v>
       </c>
       <c r="D53">
-        <v>3099.546514140496</v>
+        <v>3077.576653115867</v>
       </c>
       <c r="E53">
-        <v>1870.458</v>
+        <v>1912.316</v>
       </c>
       <c r="F53">
-        <v>2134.758</v>
+        <v>2176.616</v>
       </c>
       <c r="G53">
         <v>55.2</v>
@@ -5627,37 +5627,37 @@
         <v>197.6</v>
       </c>
       <c r="M53">
-        <v>503.3759364000001</v>
+        <v>513.2460528</v>
       </c>
       <c r="N53">
-        <v>-305.7759364000001</v>
+        <v>-315.6460528</v>
       </c>
       <c r="O53">
-        <v>-107.02157774</v>
+        <v>-110.47611848</v>
       </c>
       <c r="P53">
-        <v>-198.7543586600001</v>
+        <v>-205.16993432</v>
       </c>
       <c r="Q53">
-        <v>-128.05435866</v>
+        <v>-134.46993432</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.4249384896078697</v>
+        <v>0.432837208141367</v>
       </c>
       <c r="T53">
-        <v>1.862848509167333</v>
+        <v>1.901657853108319</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1373923443671393</v>
+        <v>0.1347501838985404</v>
       </c>
       <c r="W53">
-        <v>0.2034028851982286</v>
+        <v>0.2040259066367242</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3925495553346835</v>
+        <v>0.3850005254244013</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.3138553313589527</v>
+        <v>0.3157553313589527</v>
       </c>
       <c r="C54">
-        <v>956.1606531158668</v>
+        <v>892.6420487059281</v>
       </c>
       <c r="D54">
-        <v>3077.576653115867</v>
+        <v>3055.916048705928</v>
       </c>
       <c r="E54">
-        <v>1912.316</v>
+        <v>1954.174</v>
       </c>
       <c r="F54">
-        <v>2176.616</v>
+        <v>2218.474</v>
       </c>
       <c r="G54">
         <v>55.2</v>
@@ -5709,37 +5709,37 @@
         <v>197.6</v>
       </c>
       <c r="M54">
-        <v>513.2460528</v>
+        <v>523.1161692000001</v>
       </c>
       <c r="N54">
-        <v>-315.6460528</v>
+        <v>-325.5161692</v>
       </c>
       <c r="O54">
-        <v>-110.47611848</v>
+        <v>-113.93065922</v>
       </c>
       <c r="P54">
-        <v>-205.16993432</v>
+        <v>-211.58550998</v>
       </c>
       <c r="Q54">
-        <v>-134.46993432</v>
+        <v>-140.88550998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.432837208141367</v>
+        <v>0.4410720423571408</v>
       </c>
       <c r="T54">
-        <v>1.901657853108319</v>
+        <v>1.942118658493603</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1347501838985404</v>
+        <v>0.132207727598568</v>
       </c>
       <c r="W54">
-        <v>0.2040259066367242</v>
+        <v>0.2046254178322577</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3850005254244013</v>
+        <v>0.3777363645673371</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.3157553313589527</v>
+        <v>0.3176553313589528</v>
       </c>
       <c r="C55">
-        <v>892.6420487059281</v>
+        <v>829.4262167166962</v>
       </c>
       <c r="D55">
-        <v>3055.916048705928</v>
+        <v>3034.558216716697</v>
       </c>
       <c r="E55">
-        <v>1954.174</v>
+        <v>1996.032</v>
       </c>
       <c r="F55">
-        <v>2218.474</v>
+        <v>2260.332</v>
       </c>
       <c r="G55">
         <v>55.2</v>
@@ -5791,37 +5791,37 @@
         <v>197.6</v>
       </c>
       <c r="M55">
-        <v>523.1161692000001</v>
+        <v>532.9862856000001</v>
       </c>
       <c r="N55">
-        <v>-325.5161692</v>
+        <v>-335.3862856000001</v>
       </c>
       <c r="O55">
-        <v>-113.93065922</v>
+        <v>-117.38519996</v>
       </c>
       <c r="P55">
-        <v>-211.58550998</v>
+        <v>-218.00108564</v>
       </c>
       <c r="Q55">
-        <v>-140.88550998</v>
+        <v>-147.30108564</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.4410720423571408</v>
+        <v>0.4496649128431657</v>
       </c>
       <c r="T55">
-        <v>1.942118658493603</v>
+        <v>1.984338629330421</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.132207727598568</v>
+        <v>0.1297594363467426</v>
       </c>
       <c r="W55">
-        <v>0.2046254178322577</v>
+        <v>0.2052027249094381</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3777363645673371</v>
+        <v>0.370741246704979</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.3176553313589528</v>
+        <v>0.3195553313589528</v>
       </c>
       <c r="C56">
-        <v>829.4262167166962</v>
+        <v>766.5068529684895</v>
       </c>
       <c r="D56">
-        <v>3034.558216716697</v>
+        <v>3013.49685296849</v>
       </c>
       <c r="E56">
-        <v>1996.032</v>
+        <v>2037.890000000001</v>
       </c>
       <c r="F56">
-        <v>2260.332</v>
+        <v>2302.190000000001</v>
       </c>
       <c r="G56">
         <v>55.2</v>
@@ -5873,37 +5873,37 @@
         <v>197.6</v>
       </c>
       <c r="M56">
-        <v>532.9862856000001</v>
+        <v>542.8564020000001</v>
       </c>
       <c r="N56">
-        <v>-335.3862856000001</v>
+        <v>-345.2564020000001</v>
       </c>
       <c r="O56">
-        <v>-117.38519996</v>
+        <v>-120.8397407</v>
       </c>
       <c r="P56">
-        <v>-218.00108564</v>
+        <v>-224.4166613000001</v>
       </c>
       <c r="Q56">
-        <v>-147.30108564</v>
+        <v>-153.7166613000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.4496649128431657</v>
+        <v>0.4586396886841249</v>
       </c>
       <c r="T56">
-        <v>1.984338629330421</v>
+        <v>2.028435043315541</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1297594363467426</v>
+        <v>0.1274001738677109</v>
       </c>
       <c r="W56">
-        <v>0.2052027249094381</v>
+        <v>0.2057590390019938</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.370741246704979</v>
+        <v>0.3640004967648884</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3195553313589528</v>
+        <v>0.3214553313589528</v>
       </c>
       <c r="C57">
-        <v>766.5068529684895</v>
+        <v>703.8778270920329</v>
       </c>
       <c r="D57">
-        <v>3013.49685296849</v>
+        <v>2992.725827092033</v>
       </c>
       <c r="E57">
-        <v>2037.890000000001</v>
+        <v>2079.748</v>
       </c>
       <c r="F57">
-        <v>2302.190000000001</v>
+        <v>2344.048</v>
       </c>
       <c r="G57">
         <v>55.2</v>
@@ -5955,37 +5955,37 @@
         <v>197.6</v>
       </c>
       <c r="M57">
-        <v>542.8564020000001</v>
+        <v>552.7265184</v>
       </c>
       <c r="N57">
-        <v>-345.2564020000001</v>
+        <v>-355.1265184</v>
       </c>
       <c r="O57">
-        <v>-120.8397407</v>
+        <v>-124.29428144</v>
       </c>
       <c r="P57">
-        <v>-224.4166613000001</v>
+        <v>-230.83223696</v>
       </c>
       <c r="Q57">
-        <v>-153.7166613000001</v>
+        <v>-160.13223696</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.4586396886841249</v>
+        <v>0.4680224088814913</v>
       </c>
       <c r="T57">
-        <v>2.028435043315541</v>
+        <v>2.07453583975453</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1274001738677109</v>
+        <v>0.1251251707629304</v>
       </c>
       <c r="W57">
-        <v>0.2057590390019938</v>
+        <v>0.206295484734101</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3640004967648884</v>
+        <v>0.3575004878940869</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3214553313589528</v>
+        <v>0.3233553313589527</v>
       </c>
       <c r="C58">
-        <v>703.8778270920329</v>
+        <v>641.5331765793785</v>
       </c>
       <c r="D58">
-        <v>2992.725827092033</v>
+        <v>2972.239176579379</v>
       </c>
       <c r="E58">
-        <v>2079.748</v>
+        <v>2121.606</v>
       </c>
       <c r="F58">
-        <v>2344.048</v>
+        <v>2385.906</v>
       </c>
       <c r="G58">
         <v>55.2</v>
@@ -6037,37 +6037,37 @@
         <v>197.6</v>
       </c>
       <c r="M58">
-        <v>552.7265184</v>
+        <v>562.5966348000002</v>
       </c>
       <c r="N58">
-        <v>-355.1265184</v>
+        <v>-364.9966348000002</v>
       </c>
       <c r="O58">
-        <v>-124.29428144</v>
+        <v>-127.74882218</v>
       </c>
       <c r="P58">
-        <v>-230.83223696</v>
+        <v>-237.2478126200001</v>
       </c>
       <c r="Q58">
-        <v>-160.13223696</v>
+        <v>-166.5478126200001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4680224088814913</v>
+        <v>0.477841534669433</v>
       </c>
       <c r="T58">
-        <v>2.07453583975453</v>
+        <v>2.122780859283706</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1251251707629304</v>
+        <v>0.122929992328493</v>
       </c>
       <c r="W58">
-        <v>0.206295484734101</v>
+        <v>0.2068131078089414</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3575004878940869</v>
+        <v>0.3512285495099801</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.3233553313589527</v>
+        <v>0.3252553313589528</v>
       </c>
       <c r="C59">
-        <v>641.5331765793785</v>
+        <v>579.4671010775114</v>
       </c>
       <c r="D59">
-        <v>2972.239176579379</v>
+        <v>2952.031101077512</v>
       </c>
       <c r="E59">
-        <v>2121.606</v>
+        <v>2163.464</v>
       </c>
       <c r="F59">
-        <v>2385.906</v>
+        <v>2427.764000000001</v>
       </c>
       <c r="G59">
         <v>55.2</v>
@@ -6119,37 +6119,37 @@
         <v>197.6</v>
       </c>
       <c r="M59">
-        <v>562.5966348000002</v>
+        <v>572.4667512000002</v>
       </c>
       <c r="N59">
-        <v>-364.9966348000002</v>
+        <v>-374.8667512000002</v>
       </c>
       <c r="O59">
-        <v>-127.74882218</v>
+        <v>-131.20336292</v>
       </c>
       <c r="P59">
-        <v>-237.2478126200001</v>
+        <v>-243.6633882800001</v>
       </c>
       <c r="Q59">
-        <v>-166.5478126200001</v>
+        <v>-172.9633882800001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.477841534669433</v>
+        <v>0.4881282378758481</v>
       </c>
       <c r="T59">
-        <v>2.122780859283706</v>
+        <v>2.173323260695223</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.122929992328493</v>
+        <v>0.1208105097021397</v>
       </c>
       <c r="W59">
-        <v>0.2068131078089414</v>
+        <v>0.2073128818122355</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3512285495099801</v>
+        <v>0.3451728848632563</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.3252553313589528</v>
+        <v>0.3271553313589527</v>
       </c>
       <c r="C60">
-        <v>579.4671010775119</v>
+        <v>517.6739569131701</v>
       </c>
       <c r="D60">
-        <v>2952.031101077512</v>
+        <v>2932.09595691317</v>
       </c>
       <c r="E60">
-        <v>2163.464</v>
+        <v>2205.322</v>
       </c>
       <c r="F60">
-        <v>2427.764</v>
+        <v>2469.622</v>
       </c>
       <c r="G60">
         <v>55.2</v>
@@ -6201,37 +6201,37 @@
         <v>197.6</v>
       </c>
       <c r="M60">
-        <v>572.4667512000001</v>
+        <v>582.3368676</v>
       </c>
       <c r="N60">
-        <v>-374.8667512000001</v>
+        <v>-384.7368676</v>
       </c>
       <c r="O60">
-        <v>-131.20336292</v>
+        <v>-134.65790366</v>
       </c>
       <c r="P60">
-        <v>-243.66338828</v>
+        <v>-250.07896394</v>
       </c>
       <c r="Q60">
-        <v>-172.96338828</v>
+        <v>-179.37896394</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.488128237875848</v>
+        <v>0.4989167314825759</v>
       </c>
       <c r="T60">
-        <v>2.173323260695222</v>
+        <v>2.226331145102422</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1208105097021397</v>
+        <v>0.1187628739444763</v>
       </c>
       <c r="W60">
-        <v>0.2073128818122355</v>
+        <v>0.2077957143238925</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3451728848632563</v>
+        <v>0.3393224969842181</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.3271553313589527</v>
+        <v>0.3290553313589528</v>
       </c>
       <c r="C61">
-        <v>517.6739569131701</v>
+        <v>456.148251838008</v>
       </c>
       <c r="D61">
-        <v>2932.09595691317</v>
+        <v>2912.428251838008</v>
       </c>
       <c r="E61">
-        <v>2205.322</v>
+        <v>2247.18</v>
       </c>
       <c r="F61">
-        <v>2469.622</v>
+        <v>2511.48</v>
       </c>
       <c r="G61">
         <v>55.2</v>
@@ -6283,37 +6283,37 @@
         <v>197.6</v>
       </c>
       <c r="M61">
-        <v>582.3368676</v>
+        <v>592.206984</v>
       </c>
       <c r="N61">
-        <v>-384.7368676</v>
+        <v>-394.606984</v>
       </c>
       <c r="O61">
-        <v>-134.65790366</v>
+        <v>-138.1124444</v>
       </c>
       <c r="P61">
-        <v>-250.07896394</v>
+        <v>-256.4945396000001</v>
       </c>
       <c r="Q61">
-        <v>-179.37896394</v>
+        <v>-185.7945396</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4989167314825759</v>
+        <v>0.5102446497696405</v>
       </c>
       <c r="T61">
-        <v>2.226331145102422</v>
+        <v>2.281989423729983</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1187628739444763</v>
+        <v>0.1167834927120684</v>
       </c>
       <c r="W61">
-        <v>0.2077957143238925</v>
+        <v>0.2082624524184943</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3393224969842181</v>
+        <v>0.3336671220344811</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.3290553313589528</v>
+        <v>0.3309553313589527</v>
       </c>
       <c r="C62">
-        <v>456.148251838008</v>
+        <v>394.8846399838617</v>
       </c>
       <c r="D62">
-        <v>2912.428251838008</v>
+        <v>2893.022639983862</v>
       </c>
       <c r="E62">
-        <v>2247.18</v>
+        <v>2289.038</v>
       </c>
       <c r="F62">
-        <v>2511.48</v>
+        <v>2553.338</v>
       </c>
       <c r="G62">
         <v>55.2</v>
@@ -6365,37 +6365,37 @@
         <v>197.6</v>
       </c>
       <c r="M62">
-        <v>592.206984</v>
+        <v>602.0771004000001</v>
       </c>
       <c r="N62">
-        <v>-394.606984</v>
+        <v>-404.4771004</v>
       </c>
       <c r="O62">
-        <v>-138.1124444</v>
+        <v>-141.56698514</v>
       </c>
       <c r="P62">
-        <v>-256.4945396000001</v>
+        <v>-262.91011526</v>
       </c>
       <c r="Q62">
-        <v>-185.7945396</v>
+        <v>-192.21011526</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.5102446497696405</v>
+        <v>0.5221534869432208</v>
       </c>
       <c r="T62">
-        <v>2.281989423729983</v>
+        <v>2.340501973056393</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1167834927120684</v>
+        <v>0.1148690092249853</v>
       </c>
       <c r="W62">
-        <v>0.2082624524184943</v>
+        <v>0.2087138876247485</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3336671220344811</v>
+        <v>0.3281971692142437</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3309553313589527</v>
+        <v>0.3328553313589527</v>
       </c>
       <c r="C63">
-        <v>394.8846399838617</v>
+        <v>333.8779170183379</v>
       </c>
       <c r="D63">
-        <v>2893.022639983862</v>
+        <v>2873.873917018338</v>
       </c>
       <c r="E63">
-        <v>2289.038</v>
+        <v>2330.896</v>
       </c>
       <c r="F63">
-        <v>2553.338</v>
+        <v>2595.196</v>
       </c>
       <c r="G63">
         <v>55.2</v>
@@ -6447,37 +6447,37 @@
         <v>197.6</v>
       </c>
       <c r="M63">
-        <v>602.0771004000001</v>
+        <v>611.9472168</v>
       </c>
       <c r="N63">
-        <v>-404.4771004</v>
+        <v>-414.3472168</v>
       </c>
       <c r="O63">
-        <v>-141.56698514</v>
+        <v>-145.02152588</v>
       </c>
       <c r="P63">
-        <v>-262.91011526</v>
+        <v>-269.3256909199999</v>
       </c>
       <c r="Q63">
-        <v>-192.21011526</v>
+        <v>-198.6256909199999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.5221534869432208</v>
+        <v>0.5346891050206742</v>
       </c>
       <c r="T63">
-        <v>2.340501973056393</v>
+        <v>2.402094130242088</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1148690092249853</v>
+        <v>0.1130162832697436</v>
       </c>
       <c r="W63">
-        <v>0.2087138876247485</v>
+        <v>0.2091507604049945</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3281971692142437</v>
+        <v>0.3229036664849818</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3328553313589527</v>
+        <v>0.3347553313589527</v>
       </c>
       <c r="C64">
-        <v>333.8779170183379</v>
+        <v>273.1230154915347</v>
       </c>
       <c r="D64">
-        <v>2873.873917018338</v>
+        <v>2854.977015491535</v>
       </c>
       <c r="E64">
-        <v>2330.896</v>
+        <v>2372.754</v>
       </c>
       <c r="F64">
-        <v>2595.196</v>
+        <v>2637.054</v>
       </c>
       <c r="G64">
         <v>55.2</v>
@@ -6529,37 +6529,37 @@
         <v>197.6</v>
       </c>
       <c r="M64">
-        <v>611.9472168</v>
+        <v>621.8173332</v>
       </c>
       <c r="N64">
-        <v>-414.3472168</v>
+        <v>-424.2173332</v>
       </c>
       <c r="O64">
-        <v>-145.02152588</v>
+        <v>-148.47606662</v>
       </c>
       <c r="P64">
-        <v>-269.3256909199999</v>
+        <v>-275.74126658</v>
       </c>
       <c r="Q64">
-        <v>-198.6256909199999</v>
+        <v>-205.04126658</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.5346891050206742</v>
+        <v>0.5479023240752869</v>
       </c>
       <c r="T64">
-        <v>2.402094130242088</v>
+        <v>2.467015593221604</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1130162832697436</v>
+        <v>0.1112223740114937</v>
       </c>
       <c r="W64">
-        <v>0.2091507604049945</v>
+        <v>0.2095737642080898</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3229036664849818</v>
+        <v>0.3177782114614106</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3347553313589527</v>
+        <v>0.3366553313589528</v>
       </c>
       <c r="C65">
-        <v>273.1230154915347</v>
+        <v>212.6150003651501</v>
       </c>
       <c r="D65">
-        <v>2854.977015491535</v>
+        <v>2836.327000365151</v>
       </c>
       <c r="E65">
-        <v>2372.754</v>
+        <v>2414.612</v>
       </c>
       <c r="F65">
-        <v>2637.054</v>
+        <v>2678.912</v>
       </c>
       <c r="G65">
         <v>55.2</v>
@@ -6611,37 +6611,37 @@
         <v>197.6</v>
       </c>
       <c r="M65">
-        <v>621.8173332</v>
+        <v>631.6874496</v>
       </c>
       <c r="N65">
-        <v>-424.2173332</v>
+        <v>-434.0874496</v>
       </c>
       <c r="O65">
-        <v>-148.47606662</v>
+        <v>-151.93060736</v>
       </c>
       <c r="P65">
-        <v>-275.74126658</v>
+        <v>-282.1568422400001</v>
       </c>
       <c r="Q65">
-        <v>-205.04126658</v>
+        <v>-211.45684224</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.5479023240752869</v>
+        <v>0.5618496108551561</v>
       </c>
       <c r="T65">
-        <v>2.467015593221604</v>
+        <v>2.535543804144426</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1112223740114937</v>
+        <v>0.1094845244175641</v>
       </c>
       <c r="W65">
-        <v>0.2095737642080898</v>
+        <v>0.2099835491423384</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3177782114614106</v>
+        <v>0.3128129269073261</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3366553313589528</v>
+        <v>0.3385553313589528</v>
       </c>
       <c r="C66">
-        <v>212.6150003651501</v>
+        <v>152.3490647156832</v>
       </c>
       <c r="D66">
-        <v>2836.327000365151</v>
+        <v>2817.919064715684</v>
       </c>
       <c r="E66">
-        <v>2414.612</v>
+        <v>2456.47</v>
       </c>
       <c r="F66">
-        <v>2678.912</v>
+        <v>2720.77</v>
       </c>
       <c r="G66">
         <v>55.2</v>
@@ -6693,37 +6693,37 @@
         <v>197.6</v>
       </c>
       <c r="M66">
-        <v>631.6874496</v>
+        <v>641.5575660000002</v>
       </c>
       <c r="N66">
-        <v>-434.0874496</v>
+        <v>-443.9575660000002</v>
       </c>
       <c r="O66">
-        <v>-151.93060736</v>
+        <v>-155.3851481</v>
       </c>
       <c r="P66">
-        <v>-282.1568422400001</v>
+        <v>-288.5724179000001</v>
       </c>
       <c r="Q66">
-        <v>-211.45684224</v>
+        <v>-217.8724179000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.5618496108551561</v>
+        <v>0.5765938854510176</v>
       </c>
       <c r="T66">
-        <v>2.535543804144426</v>
+        <v>2.607987912834267</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1094845244175641</v>
+        <v>0.1078001471188323</v>
       </c>
       <c r="W66">
-        <v>0.2099835491423384</v>
+        <v>0.2103807253093793</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3128129269073261</v>
+        <v>0.308000420339521</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3385553313589528</v>
+        <v>0.3404553313589527</v>
       </c>
       <c r="C67">
-        <v>152.3490647156832</v>
+        <v>92.32052560387956</v>
       </c>
       <c r="D67">
-        <v>2817.919064715684</v>
+        <v>2799.74852560388</v>
       </c>
       <c r="E67">
-        <v>2456.47</v>
+        <v>2498.328</v>
       </c>
       <c r="F67">
-        <v>2720.77</v>
+        <v>2762.628</v>
       </c>
       <c r="G67">
         <v>55.2</v>
@@ -6775,37 +6775,37 @@
         <v>197.6</v>
       </c>
       <c r="M67">
-        <v>641.5575660000002</v>
+        <v>651.4276824000001</v>
       </c>
       <c r="N67">
-        <v>-443.9575660000002</v>
+        <v>-453.8276824000001</v>
       </c>
       <c r="O67">
-        <v>-155.3851481</v>
+        <v>-158.83968884</v>
       </c>
       <c r="P67">
-        <v>-288.5724179000001</v>
+        <v>-294.9879935600001</v>
       </c>
       <c r="Q67">
-        <v>-217.8724179000001</v>
+        <v>-224.28799356</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5765938854510176</v>
+        <v>0.5922054703172239</v>
       </c>
       <c r="T67">
-        <v>2.607987912834267</v>
+        <v>2.684693439682333</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1078001471188323</v>
+        <v>0.1061668115564258</v>
       </c>
       <c r="W67">
-        <v>0.2103807253093793</v>
+        <v>0.2107658658349948</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.308000420339521</v>
+        <v>0.3033337473040737</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3404553313589527</v>
+        <v>0.3423553313589527</v>
       </c>
       <c r="C68">
-        <v>92.32052560387956</v>
+        <v>32.52482010295034</v>
       </c>
       <c r="D68">
-        <v>2799.74852560388</v>
+        <v>2781.810820102951</v>
       </c>
       <c r="E68">
-        <v>2498.328</v>
+        <v>2540.186</v>
       </c>
       <c r="F68">
-        <v>2762.628</v>
+        <v>2804.486</v>
       </c>
       <c r="G68">
         <v>55.2</v>
@@ -6857,37 +6857,37 @@
         <v>197.6</v>
       </c>
       <c r="M68">
-        <v>651.4276824000001</v>
+        <v>661.2977988000001</v>
       </c>
       <c r="N68">
-        <v>-453.8276824000001</v>
+        <v>-463.6977988000001</v>
       </c>
       <c r="O68">
-        <v>-158.83968884</v>
+        <v>-162.29422958</v>
       </c>
       <c r="P68">
-        <v>-294.9879935600001</v>
+        <v>-301.4035692200001</v>
       </c>
       <c r="Q68">
-        <v>-224.28799356</v>
+        <v>-230.70356922</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.5922054703172239</v>
+        <v>0.6087632118419883</v>
       </c>
       <c r="T68">
-        <v>2.684693439682333</v>
+        <v>2.766047786339374</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1061668115564258</v>
+        <v>0.1045822322794642</v>
       </c>
       <c r="W68">
-        <v>0.2107658658349948</v>
+        <v>0.2111395096285024</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3033337473040737</v>
+        <v>0.2988063779413264</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3423553313589527</v>
+        <v>0.3442553313589527</v>
       </c>
       <c r="C69">
-        <v>32.52482010295034</v>
+        <v>-27.04249852148041</v>
       </c>
       <c r="D69">
-        <v>2781.810820102951</v>
+        <v>2764.10150147852</v>
       </c>
       <c r="E69">
-        <v>2540.186</v>
+        <v>2582.044</v>
       </c>
       <c r="F69">
-        <v>2804.486</v>
+        <v>2846.344000000001</v>
       </c>
       <c r="G69">
         <v>55.2</v>
@@ -6939,37 +6939,37 @@
         <v>197.6</v>
       </c>
       <c r="M69">
-        <v>661.2977988000001</v>
+        <v>671.1679152000002</v>
       </c>
       <c r="N69">
-        <v>-463.6977988000001</v>
+        <v>-473.5679152000001</v>
       </c>
       <c r="O69">
-        <v>-162.29422958</v>
+        <v>-165.74877032</v>
       </c>
       <c r="P69">
-        <v>-301.4035692200001</v>
+        <v>-307.8191448800001</v>
       </c>
       <c r="Q69">
-        <v>-230.70356922</v>
+        <v>-237.1191448800001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.6087632118419883</v>
+        <v>0.6263558122120505</v>
       </c>
       <c r="T69">
-        <v>2.766047786339374</v>
+        <v>2.852486779662479</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1045822322794642</v>
+        <v>0.1030442582753544</v>
       </c>
       <c r="W69">
-        <v>0.2111395096285024</v>
+        <v>0.2115021638986714</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2988063779413264</v>
+        <v>0.2944121665010128</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3442553313589527</v>
+        <v>0.3461553313589527</v>
       </c>
       <c r="C70">
-        <v>-27.04249852148041</v>
+        <v>-86.38576448645426</v>
       </c>
       <c r="D70">
-        <v>2764.10150147852</v>
+        <v>2746.616235513546</v>
       </c>
       <c r="E70">
-        <v>2582.044</v>
+        <v>2623.902</v>
       </c>
       <c r="F70">
-        <v>2846.344000000001</v>
+        <v>2888.202</v>
       </c>
       <c r="G70">
         <v>55.2</v>
@@ -7021,37 +7021,37 @@
         <v>197.6</v>
       </c>
       <c r="M70">
-        <v>671.1679152000002</v>
+        <v>681.0380316000001</v>
       </c>
       <c r="N70">
-        <v>-473.5679152000001</v>
+        <v>-483.4380316</v>
       </c>
       <c r="O70">
-        <v>-165.74877032</v>
+        <v>-169.20331106</v>
       </c>
       <c r="P70">
-        <v>-307.8191448800001</v>
+        <v>-314.23472054</v>
       </c>
       <c r="Q70">
-        <v>-237.1191448800001</v>
+        <v>-243.53472054</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.6263558122120505</v>
+        <v>0.6450834190576006</v>
       </c>
       <c r="T70">
-        <v>2.852486779662479</v>
+        <v>2.944502482232237</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1030442582753544</v>
+        <v>0.1015508632278855</v>
       </c>
       <c r="W70">
-        <v>0.2115021638986714</v>
+        <v>0.2118543064508646</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2944121665010128</v>
+        <v>0.2901453235082444</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3461553313589527</v>
+        <v>0.3480553313589527</v>
       </c>
       <c r="C71">
-        <v>-86.38576448645426</v>
+        <v>-145.5092030281435</v>
       </c>
       <c r="D71">
-        <v>2746.616235513546</v>
+        <v>2729.350796971857</v>
       </c>
       <c r="E71">
-        <v>2623.902</v>
+        <v>2665.76</v>
       </c>
       <c r="F71">
-        <v>2888.202</v>
+        <v>2930.06</v>
       </c>
       <c r="G71">
         <v>55.2</v>
@@ -7103,37 +7103,37 @@
         <v>197.6</v>
       </c>
       <c r="M71">
-        <v>681.0380316000001</v>
+        <v>690.9081480000001</v>
       </c>
       <c r="N71">
-        <v>-483.4380316</v>
+        <v>-493.3081480000001</v>
       </c>
       <c r="O71">
-        <v>-169.20331106</v>
+        <v>-172.6578518</v>
       </c>
       <c r="P71">
-        <v>-314.23472054</v>
+        <v>-320.6502962000001</v>
       </c>
       <c r="Q71">
-        <v>-243.53472054</v>
+        <v>-249.9502962000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.6450834190576006</v>
+        <v>0.6650595330261873</v>
       </c>
       <c r="T71">
-        <v>2.944502482232237</v>
+        <v>3.042652564973312</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1015508632278855</v>
+        <v>0.1001001366103443</v>
       </c>
       <c r="W71">
-        <v>0.2118543064508646</v>
+        <v>0.2121963877872808</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2901453235082444</v>
+        <v>0.2860003903152695</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3480553313589527</v>
+        <v>0.3499553313589527</v>
       </c>
       <c r="C72">
-        <v>-145.5092030281435</v>
+        <v>-204.4169338057591</v>
       </c>
       <c r="D72">
-        <v>2729.350796971857</v>
+        <v>2712.301066194242</v>
       </c>
       <c r="E72">
-        <v>2665.76</v>
+        <v>2707.618</v>
       </c>
       <c r="F72">
-        <v>2930.06</v>
+        <v>2971.918000000001</v>
       </c>
       <c r="G72">
         <v>55.2</v>
@@ -7185,37 +7185,37 @@
         <v>197.6</v>
       </c>
       <c r="M72">
-        <v>690.9081480000001</v>
+        <v>700.7782644000001</v>
       </c>
       <c r="N72">
-        <v>-493.3081480000001</v>
+        <v>-503.1782644000001</v>
       </c>
       <c r="O72">
-        <v>-172.6578518</v>
+        <v>-176.11239254</v>
       </c>
       <c r="P72">
-        <v>-320.6502962000001</v>
+        <v>-327.0658718600001</v>
       </c>
       <c r="Q72">
-        <v>-249.9502962000001</v>
+        <v>-256.3658718600001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.6650595330261873</v>
+        <v>0.6864133100270904</v>
       </c>
       <c r="T72">
-        <v>3.042652564973312</v>
+        <v>3.147571618937909</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1001001366103443</v>
+        <v>0.09869027553132537</v>
       </c>
       <c r="W72">
-        <v>0.2121963877872808</v>
+        <v>0.2125288330297135</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2860003903152695</v>
+        <v>0.2819722158037868</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3499553313589527</v>
+        <v>0.3518553313589527</v>
       </c>
       <c r="C73">
-        <v>-204.4169338057586</v>
+        <v>-263.1129741786767</v>
       </c>
       <c r="D73">
-        <v>2712.301066194242</v>
+        <v>2695.463025821323</v>
       </c>
       <c r="E73">
-        <v>2707.618</v>
+        <v>2749.476</v>
       </c>
       <c r="F73">
-        <v>2971.918</v>
+        <v>3013.776</v>
       </c>
       <c r="G73">
         <v>55.2</v>
@@ -7267,37 +7267,37 @@
         <v>197.6</v>
       </c>
       <c r="M73">
-        <v>700.7782644</v>
+        <v>710.6483808</v>
       </c>
       <c r="N73">
-        <v>-503.1782644</v>
+        <v>-513.0483808</v>
       </c>
       <c r="O73">
-        <v>-176.11239254</v>
+        <v>-179.56693328</v>
       </c>
       <c r="P73">
-        <v>-327.06587186</v>
+        <v>-333.48144752</v>
       </c>
       <c r="Q73">
-        <v>-256.36587186</v>
+        <v>-262.78144752</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.6864133100270902</v>
+        <v>0.7092923568137719</v>
       </c>
       <c r="T73">
-        <v>3.147571618937908</v>
+        <v>3.259984891042833</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09869027553132539</v>
+        <v>0.09731957726005697</v>
       </c>
       <c r="W73">
-        <v>0.2125288330297135</v>
+        <v>0.2128520436820786</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2819722158037868</v>
+        <v>0.2780559350287343</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3518553313589527</v>
+        <v>0.3537553313589527</v>
       </c>
       <c r="C74">
-        <v>-263.1129741786767</v>
+        <v>-321.6012423622492</v>
       </c>
       <c r="D74">
-        <v>2695.463025821323</v>
+        <v>2678.832757637751</v>
       </c>
       <c r="E74">
-        <v>2749.476</v>
+        <v>2791.334</v>
       </c>
       <c r="F74">
-        <v>3013.776</v>
+        <v>3055.634</v>
       </c>
       <c r="G74">
         <v>55.2</v>
@@ -7349,37 +7349,37 @@
         <v>197.6</v>
       </c>
       <c r="M74">
-        <v>710.6483808</v>
+        <v>720.5184972000001</v>
       </c>
       <c r="N74">
-        <v>-513.0483808</v>
+        <v>-522.9184972</v>
       </c>
       <c r="O74">
-        <v>-179.56693328</v>
+        <v>-183.02147402</v>
       </c>
       <c r="P74">
-        <v>-333.48144752</v>
+        <v>-339.89702318</v>
       </c>
       <c r="Q74">
-        <v>-262.78144752</v>
+        <v>-269.19702318</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.7092923568137719</v>
+        <v>0.7338661478068745</v>
       </c>
       <c r="T74">
-        <v>3.259984891042833</v>
+        <v>3.380725072192567</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09731957726005697</v>
+        <v>0.09598643236608359</v>
       </c>
       <c r="W74">
-        <v>0.2128520436820786</v>
+        <v>0.2131663992480775</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2780559350287343</v>
+        <v>0.2742469496173817</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3537553313589527</v>
+        <v>0.3556553313589528</v>
       </c>
       <c r="C75">
-        <v>-321.6012423622492</v>
+        <v>-379.8855604675073</v>
       </c>
       <c r="D75">
-        <v>2678.832757637751</v>
+        <v>2662.406439532493</v>
       </c>
       <c r="E75">
-        <v>2791.334</v>
+        <v>2833.192</v>
       </c>
       <c r="F75">
-        <v>3055.634</v>
+        <v>3097.492</v>
       </c>
       <c r="G75">
         <v>55.2</v>
@@ -7431,37 +7431,37 @@
         <v>197.6</v>
       </c>
       <c r="M75">
-        <v>720.5184972000001</v>
+        <v>730.3886136000001</v>
       </c>
       <c r="N75">
-        <v>-522.9184972</v>
+        <v>-532.7886136000001</v>
       </c>
       <c r="O75">
-        <v>-183.02147402</v>
+        <v>-186.47601476</v>
       </c>
       <c r="P75">
-        <v>-339.89702318</v>
+        <v>-346.3125988400001</v>
       </c>
       <c r="Q75">
-        <v>-269.19702318</v>
+        <v>-275.61259884</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.7338661478068745</v>
+        <v>0.7603302304148314</v>
       </c>
       <c r="T75">
-        <v>3.380725072192567</v>
+        <v>3.51075295958459</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09598643236608359</v>
+        <v>0.09468931841519057</v>
       </c>
       <c r="W75">
-        <v>0.2131663992480775</v>
+        <v>0.2134722587176981</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2742469496173817</v>
+        <v>0.2705409097576874</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3556553313589528</v>
+        <v>0.3575553313589527</v>
       </c>
       <c r="C76">
-        <v>-379.8855604675073</v>
+        <v>-437.9696574297018</v>
       </c>
       <c r="D76">
-        <v>2662.406439532493</v>
+        <v>2646.180342570299</v>
       </c>
       <c r="E76">
-        <v>2833.192</v>
+        <v>2875.05</v>
       </c>
       <c r="F76">
-        <v>3097.492</v>
+        <v>3139.35</v>
       </c>
       <c r="G76">
         <v>55.2</v>
@@ -7513,37 +7513,37 @@
         <v>197.6</v>
       </c>
       <c r="M76">
-        <v>730.3886136000001</v>
+        <v>740.2587300000001</v>
       </c>
       <c r="N76">
-        <v>-532.7886136000001</v>
+        <v>-542.6587300000001</v>
       </c>
       <c r="O76">
-        <v>-186.47601476</v>
+        <v>-189.9305555</v>
       </c>
       <c r="P76">
-        <v>-346.3125988400001</v>
+        <v>-352.7281745000001</v>
       </c>
       <c r="Q76">
-        <v>-275.61259884</v>
+        <v>-282.0281745000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.7603302304148314</v>
+        <v>0.7889114396314245</v>
       </c>
       <c r="T76">
-        <v>3.51075295958459</v>
+        <v>3.651183077967973</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09468931841519057</v>
+        <v>0.09342679416965469</v>
       </c>
       <c r="W76">
-        <v>0.2134722587176981</v>
+        <v>0.2137699619347954</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2705409097576874</v>
+        <v>0.2669336976275849</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3575553313589527</v>
+        <v>0.3594553313589527</v>
       </c>
       <c r="C77">
-        <v>-437.9696574297018</v>
+        <v>-495.8571718304297</v>
       </c>
       <c r="D77">
-        <v>2646.180342570299</v>
+        <v>2630.150828169571</v>
       </c>
       <c r="E77">
-        <v>2875.05</v>
+        <v>2916.908</v>
       </c>
       <c r="F77">
-        <v>3139.35</v>
+        <v>3181.208</v>
       </c>
       <c r="G77">
         <v>55.2</v>
@@ -7595,37 +7595,37 @@
         <v>197.6</v>
       </c>
       <c r="M77">
-        <v>740.2587300000001</v>
+        <v>750.1288464</v>
       </c>
       <c r="N77">
-        <v>-542.6587300000001</v>
+        <v>-552.5288464</v>
       </c>
       <c r="O77">
-        <v>-189.9305555</v>
+        <v>-193.38509624</v>
       </c>
       <c r="P77">
-        <v>-352.7281745000001</v>
+        <v>-359.14375016</v>
       </c>
       <c r="Q77">
-        <v>-282.0281745000001</v>
+        <v>-288.44375016</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.7889114396314245</v>
+        <v>0.8198744162827339</v>
       </c>
       <c r="T77">
-        <v>3.651183077967973</v>
+        <v>3.803315706216639</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09342679416965469</v>
+        <v>0.09219749424636976</v>
       </c>
       <c r="W77">
-        <v>0.2137699619347954</v>
+        <v>0.214059830856706</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2669336976275849</v>
+        <v>0.263421412132485</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3594553313589527</v>
+        <v>0.3613553313589527</v>
       </c>
       <c r="C78">
-        <v>-495.8571718304297</v>
+        <v>-553.5516546177787</v>
       </c>
       <c r="D78">
-        <v>2630.150828169571</v>
+        <v>2614.314345382222</v>
       </c>
       <c r="E78">
-        <v>2916.908</v>
+        <v>2958.766</v>
       </c>
       <c r="F78">
-        <v>3181.208</v>
+        <v>3223.066</v>
       </c>
       <c r="G78">
         <v>55.2</v>
@@ -7677,37 +7677,37 @@
         <v>197.6</v>
       </c>
       <c r="M78">
-        <v>750.1288464</v>
+        <v>759.9989628000001</v>
       </c>
       <c r="N78">
-        <v>-552.5288464</v>
+        <v>-562.3989628</v>
       </c>
       <c r="O78">
-        <v>-193.38509624</v>
+        <v>-196.83963698</v>
       </c>
       <c r="P78">
-        <v>-359.14375016</v>
+        <v>-365.55932582</v>
       </c>
       <c r="Q78">
-        <v>-288.44375016</v>
+        <v>-294.85932582</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.8198744162827339</v>
+        <v>0.8535298256863311</v>
       </c>
       <c r="T78">
-        <v>3.803315706216639</v>
+        <v>3.96867725866084</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09219749424636976</v>
+        <v>0.09100012419122211</v>
       </c>
       <c r="W78">
-        <v>0.214059830856706</v>
+        <v>0.2143421707157098</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.263421412132485</v>
+        <v>0.2600003548320632</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3613553313589527</v>
+        <v>0.3632553313589527</v>
       </c>
       <c r="C79">
-        <v>-553.5516546177787</v>
+        <v>-611.0565717288032</v>
       </c>
       <c r="D79">
-        <v>2614.314345382222</v>
+        <v>2598.667428271197</v>
       </c>
       <c r="E79">
-        <v>2958.766</v>
+        <v>3000.624</v>
       </c>
       <c r="F79">
-        <v>3223.066</v>
+        <v>3264.924</v>
       </c>
       <c r="G79">
         <v>55.2</v>
@@ -7759,37 +7759,37 @@
         <v>197.6</v>
       </c>
       <c r="M79">
-        <v>759.9989628000001</v>
+        <v>769.8690792000001</v>
       </c>
       <c r="N79">
-        <v>-562.3989628</v>
+        <v>-572.2690792000001</v>
       </c>
       <c r="O79">
-        <v>-196.83963698</v>
+        <v>-200.29417772</v>
       </c>
       <c r="P79">
-        <v>-365.55932582</v>
+        <v>-371.9749014800001</v>
       </c>
       <c r="Q79">
-        <v>-294.85932582</v>
+        <v>-301.27490148</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.8535298256863311</v>
+        <v>0.8902448177629826</v>
       </c>
       <c r="T79">
-        <v>3.96867725866084</v>
+        <v>4.149071679509061</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09100012419122211</v>
+        <v>0.08983345593236028</v>
       </c>
       <c r="W79">
-        <v>0.2143421707157098</v>
+        <v>0.2146172710911495</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2600003548320632</v>
+        <v>0.2566670169496008</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3632553313589527</v>
+        <v>0.3651553313589528</v>
       </c>
       <c r="C80">
-        <v>-611.0565717288032</v>
+        <v>-668.3753066183854</v>
       </c>
       <c r="D80">
-        <v>2598.667428271197</v>
+        <v>2583.206693381615</v>
       </c>
       <c r="E80">
-        <v>3000.624</v>
+        <v>3042.482</v>
       </c>
       <c r="F80">
-        <v>3264.924</v>
+        <v>3306.782</v>
       </c>
       <c r="G80">
         <v>55.2</v>
@@ -7841,37 +7841,37 @@
         <v>197.6</v>
       </c>
       <c r="M80">
-        <v>769.8690792000001</v>
+        <v>779.7391956</v>
       </c>
       <c r="N80">
-        <v>-572.2690792000001</v>
+        <v>-582.1391956</v>
       </c>
       <c r="O80">
-        <v>-200.29417772</v>
+        <v>-203.74871846</v>
       </c>
       <c r="P80">
-        <v>-371.9749014800001</v>
+        <v>-378.39047714</v>
       </c>
       <c r="Q80">
-        <v>-301.27490148</v>
+        <v>-307.69047714</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.8902448177629826</v>
+        <v>0.9304564757516963</v>
       </c>
       <c r="T80">
-        <v>4.149071679509061</v>
+        <v>4.346646521390446</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08983345593236028</v>
+        <v>0.0886963235787861</v>
       </c>
       <c r="W80">
-        <v>0.2146172710911495</v>
+        <v>0.2148854069001223</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2566670169496008</v>
+        <v>0.2534180673679604</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3651553313589528</v>
+        <v>0.3670553313589527</v>
       </c>
       <c r="C81">
-        <v>-668.3753066183854</v>
+        <v>-725.5111626983548</v>
       </c>
       <c r="D81">
-        <v>2583.206693381615</v>
+        <v>2567.928837301646</v>
       </c>
       <c r="E81">
-        <v>3042.482</v>
+        <v>3084.34</v>
       </c>
       <c r="F81">
-        <v>3306.782</v>
+        <v>3348.64</v>
       </c>
       <c r="G81">
         <v>55.2</v>
@@ -7923,37 +7923,37 @@
         <v>197.6</v>
       </c>
       <c r="M81">
-        <v>779.7391956</v>
+        <v>789.6093120000002</v>
       </c>
       <c r="N81">
-        <v>-582.1391956</v>
+        <v>-592.0093120000001</v>
       </c>
       <c r="O81">
-        <v>-203.74871846</v>
+        <v>-207.2032592</v>
       </c>
       <c r="P81">
-        <v>-378.39047714</v>
+        <v>-384.8060528000001</v>
       </c>
       <c r="Q81">
-        <v>-307.69047714</v>
+        <v>-314.1060528</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.9304564757516963</v>
+        <v>0.974689299539281</v>
       </c>
       <c r="T81">
-        <v>4.346646521390446</v>
+        <v>4.563978847459968</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0886963235787861</v>
+        <v>0.08758761953405127</v>
       </c>
       <c r="W81">
-        <v>0.2148854069001223</v>
+        <v>0.2151468393138707</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2534180673679604</v>
+        <v>0.2502503415258608</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3670553313589527</v>
+        <v>0.3689553313589528</v>
       </c>
       <c r="C82">
-        <v>-725.5111626983548</v>
+        <v>-782.4673656905679</v>
       </c>
       <c r="D82">
-        <v>2567.928837301646</v>
+        <v>2552.830634309433</v>
       </c>
       <c r="E82">
-        <v>3084.34</v>
+        <v>3126.198</v>
       </c>
       <c r="F82">
-        <v>3348.64</v>
+        <v>3390.498000000001</v>
       </c>
       <c r="G82">
         <v>55.2</v>
@@ -8005,37 +8005,37 @@
         <v>197.6</v>
       </c>
       <c r="M82">
-        <v>789.6093120000002</v>
+        <v>799.4794284000002</v>
       </c>
       <c r="N82">
-        <v>-592.0093120000001</v>
+        <v>-601.8794284000002</v>
       </c>
       <c r="O82">
-        <v>-207.2032592</v>
+        <v>-210.65779994</v>
       </c>
       <c r="P82">
-        <v>-384.8060528000001</v>
+        <v>-391.2216284600001</v>
       </c>
       <c r="Q82">
-        <v>-314.1060528</v>
+        <v>-320.5216284600001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.974689299539281</v>
+        <v>1.023578210041348</v>
       </c>
       <c r="T82">
-        <v>4.563978847459968</v>
+        <v>4.804188260484176</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08758761953405127</v>
+        <v>0.08650629089782841</v>
       </c>
       <c r="W82">
-        <v>0.2151468393138707</v>
+        <v>0.2154018166062921</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2502503415258608</v>
+        <v>0.2471608311366527</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3689553313589528</v>
+        <v>0.3708553313589528</v>
       </c>
       <c r="C83">
-        <v>-782.4673656905679</v>
+        <v>-839.2470658974521</v>
       </c>
       <c r="D83">
-        <v>2552.830634309433</v>
+        <v>2537.908934102548</v>
       </c>
       <c r="E83">
-        <v>3126.198</v>
+        <v>3168.056</v>
       </c>
       <c r="F83">
-        <v>3390.498000000001</v>
+        <v>3432.356</v>
       </c>
       <c r="G83">
         <v>55.2</v>
@@ -8087,37 +8087,37 @@
         <v>197.6</v>
       </c>
       <c r="M83">
-        <v>799.4794284000002</v>
+        <v>809.3495448000001</v>
       </c>
       <c r="N83">
-        <v>-601.8794284000002</v>
+        <v>-611.7495448000001</v>
       </c>
       <c r="O83">
-        <v>-210.65779994</v>
+        <v>-214.11234068</v>
       </c>
       <c r="P83">
-        <v>-391.2216284600001</v>
+        <v>-397.6372041200001</v>
       </c>
       <c r="Q83">
-        <v>-320.5216284600001</v>
+        <v>-326.93720412</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>1.023578210041348</v>
+        <v>1.077899221710312</v>
       </c>
       <c r="T83">
-        <v>4.804188260484176</v>
+        <v>5.071087608288853</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08650629089782841</v>
+        <v>0.08545133613078174</v>
       </c>
       <c r="W83">
-        <v>0.2154018166062921</v>
+        <v>0.2156505749403617</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2471608311366527</v>
+        <v>0.2441466746593765</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3708553313589528</v>
+        <v>0.3727553313589527</v>
       </c>
       <c r="C84">
-        <v>-839.2470658974521</v>
+        <v>-895.853340393398</v>
       </c>
       <c r="D84">
-        <v>2537.908934102548</v>
+        <v>2523.160659606603</v>
       </c>
       <c r="E84">
-        <v>3168.056</v>
+        <v>3209.914</v>
       </c>
       <c r="F84">
-        <v>3432.356</v>
+        <v>3474.214</v>
       </c>
       <c r="G84">
         <v>55.2</v>
@@ -8169,37 +8169,37 @@
         <v>197.6</v>
       </c>
       <c r="M84">
-        <v>809.3495448000001</v>
+        <v>819.2196612000001</v>
       </c>
       <c r="N84">
-        <v>-611.7495448000001</v>
+        <v>-621.6196612000001</v>
       </c>
       <c r="O84">
-        <v>-214.11234068</v>
+        <v>-217.56688142</v>
       </c>
       <c r="P84">
-        <v>-397.6372041200001</v>
+        <v>-404.0527797800001</v>
       </c>
       <c r="Q84">
-        <v>-326.93720412</v>
+        <v>-333.3527797800001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>1.077899221710312</v>
+        <v>1.138610940634448</v>
       </c>
       <c r="T84">
-        <v>5.071087608288853</v>
+        <v>5.369386879364668</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08545133613078174</v>
+        <v>0.08442180196053135</v>
       </c>
       <c r="W84">
-        <v>0.2156505749403617</v>
+        <v>0.2158933390977067</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2441466746593765</v>
+        <v>0.241205148458661</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3727553313589527</v>
+        <v>0.3746553313589528</v>
       </c>
       <c r="C85">
-        <v>-895.853340393398</v>
+        <v>-952.2891951401712</v>
       </c>
       <c r="D85">
-        <v>2523.160659606603</v>
+        <v>2508.58280485983</v>
       </c>
       <c r="E85">
-        <v>3209.914</v>
+        <v>3251.772</v>
       </c>
       <c r="F85">
-        <v>3474.214</v>
+        <v>3516.072000000001</v>
       </c>
       <c r="G85">
         <v>55.2</v>
@@ -8251,37 +8251,37 @@
         <v>197.6</v>
       </c>
       <c r="M85">
-        <v>819.2196612000001</v>
+        <v>829.0897776000002</v>
       </c>
       <c r="N85">
-        <v>-621.6196612000001</v>
+        <v>-631.4897776000001</v>
       </c>
       <c r="O85">
-        <v>-217.56688142</v>
+        <v>-221.02142216</v>
       </c>
       <c r="P85">
-        <v>-404.0527797800001</v>
+        <v>-410.4683554400001</v>
       </c>
       <c r="Q85">
-        <v>-333.3527797800001</v>
+        <v>-339.7683554400001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>1.138610940634448</v>
+        <v>1.206911624424102</v>
       </c>
       <c r="T85">
-        <v>5.369386879364668</v>
+        <v>5.704973559324961</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08442180196053135</v>
+        <v>0.08341678050862025</v>
       </c>
       <c r="W85">
-        <v>0.2158933390977067</v>
+        <v>0.2161303231560674</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.241205148458661</v>
+        <v>0.2383336585960579</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3746553313589528</v>
+        <v>0.3765553313589527</v>
       </c>
       <c r="C86">
-        <v>-952.2891951401707</v>
+        <v>-1008.557567029418</v>
       </c>
       <c r="D86">
-        <v>2508.58280485983</v>
+        <v>2494.172432970582</v>
       </c>
       <c r="E86">
-        <v>3251.772</v>
+        <v>3293.63</v>
       </c>
       <c r="F86">
-        <v>3516.072</v>
+        <v>3557.93</v>
       </c>
       <c r="G86">
         <v>55.2</v>
@@ -8333,37 +8333,37 @@
         <v>197.6</v>
       </c>
       <c r="M86">
-        <v>829.0897776</v>
+        <v>838.959894</v>
       </c>
       <c r="N86">
-        <v>-631.4897776</v>
+        <v>-641.3598939999999</v>
       </c>
       <c r="O86">
-        <v>-221.02142216</v>
+        <v>-224.4759629</v>
       </c>
       <c r="P86">
-        <v>-410.46835544</v>
+        <v>-416.8839311</v>
       </c>
       <c r="Q86">
-        <v>-339.7683554400001</v>
+        <v>-346.1839311</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.206911624424101</v>
+        <v>1.284319066052374</v>
       </c>
       <c r="T86">
-        <v>5.704973559324958</v>
+        <v>6.085305129946621</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08341678050862027</v>
+        <v>0.08243540662028356</v>
       </c>
       <c r="W86">
-        <v>0.2161303231560674</v>
+        <v>0.2163617311189371</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2383336585960579</v>
+        <v>0.2355297332008103</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3765553313589527</v>
+        <v>0.3784553313589527</v>
       </c>
       <c r="C87">
-        <v>-1008.557567029418</v>
+        <v>-1064.661325855181</v>
       </c>
       <c r="D87">
-        <v>2494.172432970582</v>
+        <v>2479.926674144819</v>
       </c>
       <c r="E87">
-        <v>3293.63</v>
+        <v>3335.488</v>
       </c>
       <c r="F87">
-        <v>3557.93</v>
+        <v>3599.788</v>
       </c>
       <c r="G87">
         <v>55.2</v>
@@ -8415,37 +8415,37 @@
         <v>197.6</v>
       </c>
       <c r="M87">
-        <v>838.959894</v>
+        <v>848.8300104</v>
       </c>
       <c r="N87">
-        <v>-641.3598939999999</v>
+        <v>-651.2300104</v>
       </c>
       <c r="O87">
-        <v>-224.4759629</v>
+        <v>-227.93050364</v>
       </c>
       <c r="P87">
-        <v>-416.8839311</v>
+        <v>-423.29950676</v>
       </c>
       <c r="Q87">
-        <v>-346.1839311</v>
+        <v>-352.5995067599999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.284319066052374</v>
+        <v>1.372784713627544</v>
       </c>
       <c r="T87">
-        <v>6.085305129946621</v>
+        <v>6.519969782085666</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08243540662028356</v>
+        <v>0.08147685538051282</v>
       </c>
       <c r="W87">
-        <v>0.2163617311189371</v>
+        <v>0.2165877575012751</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2355297332008103</v>
+        <v>0.2327910153728938</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3784553313589527</v>
+        <v>0.3803553313589527</v>
       </c>
       <c r="C88">
-        <v>-1064.661325855181</v>
+        <v>-1120.603276219194</v>
       </c>
       <c r="D88">
-        <v>2479.926674144819</v>
+        <v>2465.842723780807</v>
       </c>
       <c r="E88">
-        <v>3335.488</v>
+        <v>3377.346</v>
       </c>
       <c r="F88">
-        <v>3599.788</v>
+        <v>3641.646</v>
       </c>
       <c r="G88">
         <v>55.2</v>
@@ -8497,37 +8497,37 @@
         <v>197.6</v>
       </c>
       <c r="M88">
-        <v>848.8300104</v>
+        <v>858.7001268000001</v>
       </c>
       <c r="N88">
-        <v>-651.2300104</v>
+        <v>-661.1001268000001</v>
       </c>
       <c r="O88">
-        <v>-227.93050364</v>
+        <v>-231.38504438</v>
       </c>
       <c r="P88">
-        <v>-423.29950676</v>
+        <v>-429.7150824200001</v>
       </c>
       <c r="Q88">
-        <v>-352.5995067599999</v>
+        <v>-359.0150824200001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.372784713627544</v>
+        <v>1.474860460829663</v>
       </c>
       <c r="T88">
-        <v>6.519969782085666</v>
+        <v>7.021505919169178</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08147685538051282</v>
+        <v>0.08054033980142646</v>
       </c>
       <c r="W88">
-        <v>0.2165877575012751</v>
+        <v>0.2168085878748236</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2327910153728938</v>
+        <v>0.2301152565755042</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3803553313589527</v>
+        <v>0.3822553313589527</v>
       </c>
       <c r="C89">
-        <v>-1120.603276219194</v>
+        <v>-1176.386159371618</v>
       </c>
       <c r="D89">
-        <v>2465.842723780807</v>
+        <v>2451.917840628383</v>
       </c>
       <c r="E89">
-        <v>3377.346</v>
+        <v>3419.204</v>
       </c>
       <c r="F89">
-        <v>3641.646</v>
+        <v>3683.504</v>
       </c>
       <c r="G89">
         <v>55.2</v>
@@ -8579,37 +8579,37 @@
         <v>197.6</v>
       </c>
       <c r="M89">
-        <v>858.7001268000001</v>
+        <v>868.5702432000002</v>
       </c>
       <c r="N89">
-        <v>-661.1001268000001</v>
+        <v>-670.9702432000001</v>
       </c>
       <c r="O89">
-        <v>-231.38504438</v>
+        <v>-234.83958512</v>
       </c>
       <c r="P89">
-        <v>-429.7150824200001</v>
+        <v>-436.1306580800001</v>
       </c>
       <c r="Q89">
-        <v>-359.0150824200001</v>
+        <v>-365.4306580800001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.474860460829663</v>
+        <v>1.593948832565468</v>
       </c>
       <c r="T89">
-        <v>7.021505919169178</v>
+        <v>7.606631412433278</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08054033980142646</v>
+        <v>0.07962510866731932</v>
       </c>
       <c r="W89">
-        <v>0.2168085878748236</v>
+        <v>0.2170243993762461</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2301152565755042</v>
+        <v>0.2275003104780553</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3822553313589527</v>
+        <v>0.3841553313589527</v>
       </c>
       <c r="C90">
-        <v>-1176.386159371618</v>
+        <v>-1232.012654989769</v>
       </c>
       <c r="D90">
-        <v>2451.917840628383</v>
+        <v>2438.149345010232</v>
       </c>
       <c r="E90">
-        <v>3419.204</v>
+        <v>3461.062</v>
       </c>
       <c r="F90">
-        <v>3683.504</v>
+        <v>3725.362</v>
       </c>
       <c r="G90">
         <v>55.2</v>
@@ -8661,37 +8661,37 @@
         <v>197.6</v>
       </c>
       <c r="M90">
-        <v>868.5702432000002</v>
+        <v>878.4403596000001</v>
       </c>
       <c r="N90">
-        <v>-670.9702432000001</v>
+        <v>-680.8403596000001</v>
       </c>
       <c r="O90">
-        <v>-234.83958512</v>
+        <v>-238.29412586</v>
       </c>
       <c r="P90">
-        <v>-436.1306580800001</v>
+        <v>-442.54623374</v>
       </c>
       <c r="Q90">
-        <v>-365.4306580800001</v>
+        <v>-371.84623374</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.593948832565468</v>
+        <v>1.734689635525965</v>
       </c>
       <c r="T90">
-        <v>7.606631412433278</v>
+        <v>8.298143359018122</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07962510866731932</v>
+        <v>0.07873044452498991</v>
       </c>
       <c r="W90">
-        <v>0.2170243993762461</v>
+        <v>0.2172353611810074</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2275003104780553</v>
+        <v>0.2249441272142569</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3841553313589527</v>
+        <v>0.3860553313589528</v>
       </c>
       <c r="C91">
-        <v>-1232.012654989769</v>
+        <v>-1287.485382897243</v>
       </c>
       <c r="D91">
-        <v>2438.149345010232</v>
+        <v>2424.534617102758</v>
       </c>
       <c r="E91">
-        <v>3461.062</v>
+        <v>3502.92</v>
       </c>
       <c r="F91">
-        <v>3725.362</v>
+        <v>3767.22</v>
       </c>
       <c r="G91">
         <v>55.2</v>
@@ -8743,37 +8743,37 @@
         <v>197.6</v>
       </c>
       <c r="M91">
-        <v>878.4403596000001</v>
+        <v>888.3104760000001</v>
       </c>
       <c r="N91">
-        <v>-680.8403596000001</v>
+        <v>-690.7104760000001</v>
       </c>
       <c r="O91">
-        <v>-238.29412586</v>
+        <v>-241.7486666</v>
       </c>
       <c r="P91">
-        <v>-442.54623374</v>
+        <v>-448.9618094000001</v>
       </c>
       <c r="Q91">
-        <v>-371.84623374</v>
+        <v>-378.2618094000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.734689635525965</v>
+        <v>1.903578599078562</v>
       </c>
       <c r="T91">
-        <v>8.298143359018122</v>
+        <v>9.127957694919935</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07873044452498991</v>
+        <v>0.07785566180804557</v>
       </c>
       <c r="W91">
-        <v>0.2172353611810074</v>
+        <v>0.2174416349456628</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2249441272142569</v>
+        <v>0.2224447480229874</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3860553313589528</v>
+        <v>0.3879553313589528</v>
       </c>
       <c r="C92">
-        <v>-1287.485382897243</v>
+        <v>-1342.806904725762</v>
       </c>
       <c r="D92">
-        <v>2424.534617102758</v>
+        <v>2411.071095274239</v>
       </c>
       <c r="E92">
-        <v>3502.92</v>
+        <v>3544.778</v>
       </c>
       <c r="F92">
-        <v>3767.22</v>
+        <v>3809.078</v>
       </c>
       <c r="G92">
         <v>55.2</v>
@@ -8825,37 +8825,37 @@
         <v>197.6</v>
       </c>
       <c r="M92">
-        <v>888.3104760000001</v>
+        <v>898.1805924000001</v>
       </c>
       <c r="N92">
-        <v>-690.7104760000001</v>
+        <v>-700.5805924000001</v>
       </c>
       <c r="O92">
-        <v>-241.7486666</v>
+        <v>-245.20320734</v>
       </c>
       <c r="P92">
-        <v>-448.9618094000001</v>
+        <v>-455.3773850600001</v>
       </c>
       <c r="Q92">
-        <v>-378.2618094000001</v>
+        <v>-384.67738506</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.903578599078562</v>
+        <v>2.109998443420625</v>
       </c>
       <c r="T92">
-        <v>9.127957694919935</v>
+        <v>10.14217521657771</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07785566180804557</v>
+        <v>0.07700010508488023</v>
       </c>
       <c r="W92">
-        <v>0.2174416349456628</v>
+        <v>0.2176433752209853</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2224447480229874</v>
+        <v>0.220000300242515</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3879553313589528</v>
+        <v>0.3898553313589527</v>
       </c>
       <c r="C93">
-        <v>-1342.806904725762</v>
+        <v>-1397.979725521959</v>
       </c>
       <c r="D93">
-        <v>2411.071095274239</v>
+        <v>2397.756274478041</v>
       </c>
       <c r="E93">
-        <v>3544.778</v>
+        <v>3586.636</v>
       </c>
       <c r="F93">
-        <v>3809.078</v>
+        <v>3850.936</v>
       </c>
       <c r="G93">
         <v>55.2</v>
@@ -8907,37 +8907,37 @@
         <v>197.6</v>
       </c>
       <c r="M93">
-        <v>898.1805924000001</v>
+        <v>908.0507088000001</v>
       </c>
       <c r="N93">
-        <v>-700.5805924000001</v>
+        <v>-710.4507088</v>
       </c>
       <c r="O93">
-        <v>-245.20320734</v>
+        <v>-248.65774808</v>
       </c>
       <c r="P93">
-        <v>-455.3773850600001</v>
+        <v>-461.79296072</v>
       </c>
       <c r="Q93">
-        <v>-384.67738506</v>
+        <v>-391.09296072</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>2.109998443420625</v>
+        <v>2.368023248848203</v>
       </c>
       <c r="T93">
-        <v>10.14217521657771</v>
+        <v>11.40994711864992</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07700010508488023</v>
+        <v>0.07616314742091415</v>
       </c>
       <c r="W93">
-        <v>0.2176433752209853</v>
+        <v>0.2178407298381485</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.220000300242515</v>
+        <v>0.2176089926311834</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3898553313589527</v>
+        <v>0.3917553313589527</v>
       </c>
       <c r="C94">
-        <v>-1397.979725521959</v>
+        <v>-1453.006295301222</v>
       </c>
       <c r="D94">
-        <v>2397.756274478041</v>
+        <v>2384.587704698778</v>
       </c>
       <c r="E94">
-        <v>3586.636</v>
+        <v>3628.494</v>
       </c>
       <c r="F94">
-        <v>3850.936</v>
+        <v>3892.794</v>
       </c>
       <c r="G94">
         <v>55.2</v>
@@ -8989,37 +8989,37 @@
         <v>197.6</v>
       </c>
       <c r="M94">
-        <v>908.0507088000001</v>
+        <v>917.9208252000001</v>
       </c>
       <c r="N94">
-        <v>-710.4507088</v>
+        <v>-720.3208252000001</v>
       </c>
       <c r="O94">
-        <v>-248.65774808</v>
+        <v>-252.11228882</v>
       </c>
       <c r="P94">
-        <v>-461.79296072</v>
+        <v>-468.2085363800001</v>
       </c>
       <c r="Q94">
-        <v>-391.09296072</v>
+        <v>-397.50853638</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.368023248848203</v>
+        <v>2.699769427255089</v>
       </c>
       <c r="T94">
-        <v>11.40994711864992</v>
+        <v>13.03993956417134</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07616314742091415</v>
+        <v>0.07534418884649571</v>
       </c>
       <c r="W94">
-        <v>0.2178407298381485</v>
+        <v>0.2180338402699963</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2176089926311834</v>
+        <v>0.2152691109899878</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3917553313589527</v>
+        <v>0.3936553313589527</v>
       </c>
       <c r="C95">
-        <v>-1453.006295301222</v>
+        <v>-1507.889010550598</v>
       </c>
       <c r="D95">
-        <v>2384.587704698778</v>
+        <v>2371.562989449403</v>
       </c>
       <c r="E95">
-        <v>3628.494</v>
+        <v>3670.352</v>
       </c>
       <c r="F95">
-        <v>3892.794</v>
+        <v>3934.652</v>
       </c>
       <c r="G95">
         <v>55.2</v>
@@ -9071,37 +9071,37 @@
         <v>197.6</v>
       </c>
       <c r="M95">
-        <v>917.9208252000001</v>
+        <v>927.7909416000001</v>
       </c>
       <c r="N95">
-        <v>-720.3208252000001</v>
+        <v>-730.1909416000001</v>
       </c>
       <c r="O95">
-        <v>-252.11228882</v>
+        <v>-255.56682956</v>
       </c>
       <c r="P95">
-        <v>-468.2085363800001</v>
+        <v>-474.6241120400001</v>
       </c>
       <c r="Q95">
-        <v>-397.50853638</v>
+        <v>-403.9241120400001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.699769427255089</v>
+        <v>3.142097665130938</v>
       </c>
       <c r="T95">
-        <v>13.03993956417134</v>
+        <v>15.21326282486657</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07534418884649571</v>
+        <v>0.07454265492259683</v>
       </c>
       <c r="W95">
-        <v>0.2180338402699963</v>
+        <v>0.2182228419692517</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2152691109899878</v>
+        <v>0.2129790140645624</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3936553313589527</v>
+        <v>0.3955553313589528</v>
       </c>
       <c r="C96">
-        <v>-1507.889010550598</v>
+        <v>-1562.63021568273</v>
       </c>
       <c r="D96">
-        <v>2371.562989449403</v>
+        <v>2358.679784317271</v>
       </c>
       <c r="E96">
-        <v>3670.352</v>
+        <v>3712.21</v>
       </c>
       <c r="F96">
-        <v>3934.652</v>
+        <v>3976.510000000001</v>
       </c>
       <c r="G96">
         <v>55.2</v>
@@ -9153,37 +9153,37 @@
         <v>197.6</v>
       </c>
       <c r="M96">
-        <v>927.7909416000001</v>
+        <v>937.6610580000003</v>
       </c>
       <c r="N96">
-        <v>-730.1909416000001</v>
+        <v>-740.0610580000002</v>
       </c>
       <c r="O96">
-        <v>-255.56682956</v>
+        <v>-259.0213703000001</v>
       </c>
       <c r="P96">
-        <v>-474.6241120400001</v>
+        <v>-481.0396877000002</v>
       </c>
       <c r="Q96">
-        <v>-403.9241120400001</v>
+        <v>-410.3396877000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>3.142097665130938</v>
+        <v>3.761357198157128</v>
       </c>
       <c r="T96">
-        <v>15.21326282486657</v>
+        <v>18.25591538983989</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07454265492259683</v>
+        <v>0.07375799539709579</v>
       </c>
       <c r="W96">
-        <v>0.2182228419692517</v>
+        <v>0.2184078646853648</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2129790140645624</v>
+        <v>0.210737129705988</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3955553313589528</v>
+        <v>0.3974553313589528</v>
       </c>
       <c r="C97">
-        <v>-1562.63021568273</v>
+        <v>-1617.232204442645</v>
       </c>
       <c r="D97">
-        <v>2358.679784317271</v>
+        <v>2345.935795557356</v>
       </c>
       <c r="E97">
-        <v>3712.21</v>
+        <v>3754.068</v>
       </c>
       <c r="F97">
-        <v>3976.510000000001</v>
+        <v>4018.368</v>
       </c>
       <c r="G97">
         <v>55.2</v>
@@ -9235,37 +9235,37 @@
         <v>197.6</v>
       </c>
       <c r="M97">
-        <v>937.6610580000003</v>
+        <v>947.5311744000002</v>
       </c>
       <c r="N97">
-        <v>-740.0610580000002</v>
+        <v>-749.9311744000001</v>
       </c>
       <c r="O97">
-        <v>-259.0213703000001</v>
+        <v>-262.47591104</v>
       </c>
       <c r="P97">
-        <v>-481.0396877000002</v>
+        <v>-487.4552633600001</v>
       </c>
       <c r="Q97">
-        <v>-410.3396877000001</v>
+        <v>-416.7552633600001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.761357198157128</v>
+        <v>4.690246497696413</v>
       </c>
       <c r="T97">
-        <v>18.25591538983989</v>
+        <v>22.81989423729988</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07375799539709579</v>
+        <v>0.07298968294504272</v>
       </c>
       <c r="W97">
-        <v>0.2184078646853648</v>
+        <v>0.2185890327615589</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.210737129705988</v>
+        <v>0.2085419512715507</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3974553313589527</v>
+        <v>0.3993553313589527</v>
       </c>
       <c r="C98">
-        <v>-1617.232204442644</v>
+        <v>-1671.697221269195</v>
       </c>
       <c r="D98">
-        <v>2345.935795557356</v>
+        <v>2333.328778730805</v>
       </c>
       <c r="E98">
-        <v>3754.068</v>
+        <v>3795.926</v>
       </c>
       <c r="F98">
-        <v>4018.368</v>
+        <v>4060.226</v>
       </c>
       <c r="G98">
         <v>55.2</v>
@@ -9317,37 +9317,37 @@
         <v>197.6</v>
       </c>
       <c r="M98">
-        <v>947.5311744000001</v>
+        <v>957.4012908000001</v>
       </c>
       <c r="N98">
-        <v>-749.9311744</v>
+        <v>-759.8012908000001</v>
       </c>
       <c r="O98">
-        <v>-262.47591104</v>
+        <v>-265.93045178</v>
       </c>
       <c r="P98">
-        <v>-487.4552633600001</v>
+        <v>-493.8708390200001</v>
       </c>
       <c r="Q98">
-        <v>-416.7552633600001</v>
+        <v>-423.17083902</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.6902464976964</v>
+        <v>6.238395330261867</v>
       </c>
       <c r="T98">
-        <v>22.81989423729981</v>
+        <v>30.42652564973309</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07298968294504272</v>
+        <v>0.07223721198684642</v>
       </c>
       <c r="W98">
-        <v>0.2185890327615589</v>
+        <v>0.2187664654135016</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2085419512715507</v>
+        <v>0.2063920342481327</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3993553313589527</v>
+        <v>0.4012553313589527</v>
       </c>
       <c r="C99">
-        <v>-1671.697221269195</v>
+        <v>-1726.027462612824</v>
       </c>
       <c r="D99">
-        <v>2333.328778730805</v>
+        <v>2320.856537387176</v>
       </c>
       <c r="E99">
-        <v>3795.926</v>
+        <v>3837.784</v>
       </c>
       <c r="F99">
-        <v>4060.226</v>
+        <v>4102.084</v>
       </c>
       <c r="G99">
         <v>55.2</v>
@@ -9399,37 +9399,37 @@
         <v>197.6</v>
       </c>
       <c r="M99">
-        <v>957.4012908000001</v>
+        <v>967.2714072</v>
       </c>
       <c r="N99">
-        <v>-759.8012908000001</v>
+        <v>-769.6714072</v>
       </c>
       <c r="O99">
-        <v>-265.93045178</v>
+        <v>-269.38499252</v>
       </c>
       <c r="P99">
-        <v>-493.8708390200001</v>
+        <v>-500.28641468</v>
       </c>
       <c r="Q99">
-        <v>-423.17083902</v>
+        <v>-429.58641468</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>6.238395330261867</v>
+        <v>9.3346929953928</v>
       </c>
       <c r="T99">
-        <v>30.42652564973309</v>
+        <v>45.63978847459963</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07223721198684642</v>
+        <v>0.07150009757881737</v>
       </c>
       <c r="W99">
-        <v>0.2187664654135016</v>
+        <v>0.2189402769909149</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2063920342481327</v>
+        <v>0.2042859930823354</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.4012553313589527</v>
+        <v>0.4031553313589528</v>
       </c>
       <c r="C100">
-        <v>-1726.027462612824</v>
+        <v>-1780.225078211301</v>
       </c>
       <c r="D100">
-        <v>2320.856537387176</v>
+        <v>2308.5169217887</v>
       </c>
       <c r="E100">
-        <v>3837.784</v>
+        <v>3879.642</v>
       </c>
       <c r="F100">
-        <v>4102.084</v>
+        <v>4143.942</v>
       </c>
       <c r="G100">
         <v>55.2</v>
@@ -9481,37 +9481,37 @@
         <v>197.6</v>
       </c>
       <c r="M100">
-        <v>967.2714072</v>
+        <v>977.1415236</v>
       </c>
       <c r="N100">
-        <v>-769.6714072</v>
+        <v>-779.5415236</v>
       </c>
       <c r="O100">
-        <v>-269.38499252</v>
+        <v>-272.83953326</v>
       </c>
       <c r="P100">
-        <v>-500.28641468</v>
+        <v>-506.70199034</v>
       </c>
       <c r="Q100">
-        <v>-429.58641468</v>
+        <v>-436.00199034</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>9.3346929953928</v>
+        <v>18.6235859907856</v>
       </c>
       <c r="T100">
-        <v>45.63978847459963</v>
+        <v>91.27957694919925</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07150009757881737</v>
+        <v>0.07077787437095052</v>
       </c>
       <c r="W100">
-        <v>0.2189402769909149</v>
+        <v>0.2191105772233299</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2042859930823354</v>
+        <v>0.2022224982027159</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.4031553313589528</v>
-      </c>
-      <c r="C101">
-        <v>-1780.225078211301</v>
-      </c>
-      <c r="D101">
-        <v>2308.5169217887</v>
-      </c>
-      <c r="E101">
-        <v>3879.642</v>
-      </c>
-      <c r="F101">
-        <v>4143.942</v>
-      </c>
-      <c r="G101">
-        <v>55.2</v>
-      </c>
-      <c r="H101">
-        <v>3921.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>268.3</v>
-      </c>
-      <c r="K101">
-        <v>70.70000000000002</v>
-      </c>
-      <c r="L101">
-        <v>197.6</v>
-      </c>
-      <c r="M101">
-        <v>977.1415236</v>
-      </c>
-      <c r="N101">
-        <v>-779.5415236</v>
-      </c>
-      <c r="O101">
-        <v>-272.83953326</v>
-      </c>
-      <c r="P101">
-        <v>-506.70199034</v>
-      </c>
-      <c r="Q101">
-        <v>-436.00199034</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>18.6235859907856</v>
-      </c>
-      <c r="T101">
-        <v>91.27957694919925</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07077787437095052</v>
-      </c>
-      <c r="W101">
-        <v>0.2191105772233299</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2022224982027159</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
